--- a/mainWidget/mainWidget/src/database/推进剂材料.xlsx
+++ b/mainWidget/mainWidget/src/database/推进剂材料.xlsx
@@ -5,17 +5,17 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\VSProject\gfapp_new\gfapp\mainWidget\mainWidget\src\database\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\VSProject\git\GFApp\mainWidget\mainWidget\src\database\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{38A1CF29-C229-4B1F-BAD3-A1A925AE618A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C0751E53-EBC6-42F6-BEDC-AB82A7C43E2C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-103" yWindow="-103" windowWidth="22149" windowHeight="13320" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="124519"/>
+  <calcPr calcId="191029"/>
 </workbook>
 </file>
 
@@ -121,7 +121,21 @@
         <family val="3"/>
         <charset val="134"/>
       </rPr>
-      <t>杨氏模量</t>
+      <t>泊松比</t>
+    </r>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="仿宋"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>发火温度</t>
     </r>
     <r>
       <rPr>
@@ -131,11 +145,8 @@
         <rFont val="Times New Roman"/>
         <family val="1"/>
       </rPr>
-      <t>[Pa]</t>
-    </r>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
+      <t>[</t>
+    </r>
     <r>
       <rPr>
         <b/>
@@ -145,21 +156,7 @@
         <family val="3"/>
         <charset val="134"/>
       </rPr>
-      <t>泊松比</t>
-    </r>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="仿宋"/>
-        <family val="3"/>
-        <charset val="134"/>
-      </rPr>
-      <t>发火温度</t>
+      <t>℃</t>
     </r>
     <r>
       <rPr>
@@ -169,8 +166,11 @@
         <rFont val="Times New Roman"/>
         <family val="1"/>
       </rPr>
-      <t>[</t>
-    </r>
+      <t>]</t>
+    </r>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
     <r>
       <rPr>
         <b/>
@@ -180,7 +180,7 @@
         <family val="3"/>
         <charset val="134"/>
       </rPr>
-      <t>℃</t>
+      <t>发火超压</t>
     </r>
     <r>
       <rPr>
@@ -190,7 +190,7 @@
         <rFont val="Times New Roman"/>
         <family val="1"/>
       </rPr>
-      <t>]</t>
+      <t>[MPa]</t>
     </r>
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
@@ -204,7 +204,7 @@
         <family val="3"/>
         <charset val="134"/>
       </rPr>
-      <t>发火超压</t>
+      <t>热导率</t>
     </r>
     <r>
       <rPr>
@@ -214,7 +214,7 @@
         <rFont val="Times New Roman"/>
         <family val="1"/>
       </rPr>
-      <t>[MPa]</t>
+      <t>[W/m K]</t>
     </r>
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
@@ -228,7 +228,7 @@
         <family val="3"/>
         <charset val="134"/>
       </rPr>
-      <t>热导率</t>
+      <t>比热容</t>
     </r>
     <r>
       <rPr>
@@ -238,153 +238,167 @@
         <rFont val="Times New Roman"/>
         <family val="1"/>
       </rPr>
-      <t>[W/m K]</t>
+      <t>[J/kg K]</t>
     </r>
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="仿宋"/>
-        <family val="3"/>
-        <charset val="134"/>
-      </rPr>
-      <t>比热容</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
+    <t>I</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>a</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>b</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>c</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>d</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>G1</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>e</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>g</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>x</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>y</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>z</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>G2</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>PBX-9404</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="仿宋"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>三组元</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="仿宋"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>丁羟三组元</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="仿宋"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>丁羟四组元</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="仿宋"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>四组元</t>
+    </r>
+  </si>
+  <si>
+    <t>N15</t>
+  </si>
+  <si>
+    <t>H16</t>
+  </si>
+  <si>
+    <r>
+      <t>AP/HTPB</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="仿宋"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>（高氯酸铵</t>
+    </r>
+    <r>
+      <rPr>
         <sz val="12"/>
         <color theme="1"/>
         <rFont val="Times New Roman"/>
         <family val="1"/>
       </rPr>
-      <t>[J/kg K]</t>
-    </r>
+      <t xml:space="preserve"> / </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="仿宋"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>端羟基聚丁二烯）</t>
+    </r>
+  </si>
+  <si>
+    <t>二组元</t>
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
-    <t>I</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>a</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>b</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>c</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>d</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>G1</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>e</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>g</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>x</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>y</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>z</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>G2</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>PBX-9404</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="仿宋"/>
-        <family val="3"/>
-        <charset val="134"/>
-      </rPr>
-      <t>三组元</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="仿宋"/>
-        <family val="3"/>
-        <charset val="134"/>
-      </rPr>
-      <t>丁羟三组元</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="仿宋"/>
-        <family val="3"/>
-        <charset val="134"/>
-      </rPr>
-      <t>丁羟四组元</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="仿宋"/>
-        <family val="3"/>
-        <charset val="134"/>
-      </rPr>
-      <t>四组元</t>
-    </r>
-  </si>
-  <si>
-    <t>N15</t>
-  </si>
-  <si>
-    <t>H16</t>
-  </si>
-  <si>
-    <r>
-      <t>AP/HTPB</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="仿宋"/>
-        <family val="3"/>
-        <charset val="134"/>
-      </rPr>
-      <t>（高氯酸铵</t>
+    <r>
+      <t>Al/AP/HTPB</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="仿宋"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>（铝粉</t>
     </r>
     <r>
       <rPr>
@@ -403,26 +417,7 @@
         <family val="3"/>
         <charset val="134"/>
       </rPr>
-      <t>端羟基聚丁二烯）</t>
-    </r>
-  </si>
-  <si>
-    <t>二组元</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <t>Al/AP/HTPB</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="仿宋"/>
-        <family val="3"/>
-        <charset val="134"/>
-      </rPr>
-      <t>（铝粉</t>
+      <t>高氯酸铵</t>
     </r>
     <r>
       <rPr>
@@ -441,7 +436,22 @@
         <family val="3"/>
         <charset val="134"/>
       </rPr>
-      <t>高氯酸铵</t>
+      <t>端羟基聚丁二烯）</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>NG/NC</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="仿宋"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>（硝化甘油</t>
     </r>
     <r>
       <rPr>
@@ -460,22 +470,22 @@
         <family val="3"/>
         <charset val="134"/>
       </rPr>
-      <t>端羟基聚丁二烯）</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>NG/NC</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="仿宋"/>
-        <family val="3"/>
-        <charset val="134"/>
-      </rPr>
-      <t>（硝化甘油</t>
+      <t>硝化棉）</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>CL-20/HTPB</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="仿宋"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>（六硝基六氮杂异伍兹烷</t>
     </r>
     <r>
       <rPr>
@@ -494,22 +504,22 @@
         <family val="3"/>
         <charset val="134"/>
       </rPr>
-      <t>硝化棉）</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>CL-20/HTPB</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="仿宋"/>
-        <family val="3"/>
-        <charset val="134"/>
-      </rPr>
-      <t>（六硝基六氮杂异伍兹烷</t>
+      <t>端羟基聚丁二烯）</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>ADN/HTPB</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="仿宋"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>（二硝酰胺铵</t>
     </r>
     <r>
       <rPr>
@@ -533,17 +543,17 @@
   </si>
   <si>
     <r>
-      <t>ADN/HTPB</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="仿宋"/>
-        <family val="3"/>
-        <charset val="134"/>
-      </rPr>
-      <t>（二硝酰胺铵</t>
+      <t>HMX/HTPB</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="仿宋"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>（奥克托今</t>
     </r>
     <r>
       <rPr>
@@ -567,17 +577,17 @@
   </si>
   <si>
     <r>
-      <t>HMX/HTPB</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="仿宋"/>
-        <family val="3"/>
-        <charset val="134"/>
-      </rPr>
-      <t>（奥克托今</t>
+      <t>GAP/Al</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="仿宋"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>（聚叠氮缩水甘油醚</t>
     </r>
     <r>
       <rPr>
@@ -596,22 +606,22 @@
         <family val="3"/>
         <charset val="134"/>
       </rPr>
-      <t>端羟基聚丁二烯）</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>GAP/Al</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="仿宋"/>
-        <family val="3"/>
-        <charset val="134"/>
-      </rPr>
-      <t>（聚叠氮缩水甘油醚</t>
+      <t>铝粉）</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>FOX-7/HTPB</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="仿宋"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>（</t>
     </r>
     <r>
       <rPr>
@@ -620,32 +630,17 @@
         <rFont val="Times New Roman"/>
         <family val="1"/>
       </rPr>
-      <t xml:space="preserve"> / </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="仿宋"/>
-        <family val="3"/>
-        <charset val="134"/>
-      </rPr>
-      <t>铝粉）</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>FOX-7/HTPB</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="仿宋"/>
-        <family val="3"/>
-        <charset val="134"/>
-      </rPr>
-      <t>（</t>
+      <t xml:space="preserve">1,1 - </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="仿宋"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>二氨基</t>
     </r>
     <r>
       <rPr>
@@ -654,17 +649,17 @@
         <rFont val="Times New Roman"/>
         <family val="1"/>
       </rPr>
-      <t xml:space="preserve">1,1 - </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="仿宋"/>
-        <family val="3"/>
-        <charset val="134"/>
-      </rPr>
-      <t>二氨基</t>
+      <t xml:space="preserve"> - 2,2 - </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="仿宋"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>二硝基乙烯</t>
     </r>
     <r>
       <rPr>
@@ -673,17 +668,32 @@
         <rFont val="Times New Roman"/>
         <family val="1"/>
       </rPr>
-      <t xml:space="preserve"> - 2,2 - </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="仿宋"/>
-        <family val="3"/>
-        <charset val="134"/>
-      </rPr>
-      <t>二硝基乙烯</t>
+      <t xml:space="preserve"> / </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="仿宋"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>端羟基聚丁二烯）</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>BTTN/HTPB</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="仿宋"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>（三羟甲基乙烷三硝酸酯</t>
     </r>
     <r>
       <rPr>
@@ -707,17 +717,17 @@
   </si>
   <si>
     <r>
-      <t>BTTN/HTPB</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="仿宋"/>
-        <family val="3"/>
-        <charset val="134"/>
-      </rPr>
-      <t>（三羟甲基乙烷三硝酸酯</t>
+      <t>NTO/HTPB</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="仿宋"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>（</t>
     </r>
     <r>
       <rPr>
@@ -726,32 +736,17 @@
         <rFont val="Times New Roman"/>
         <family val="1"/>
       </rPr>
-      <t xml:space="preserve"> / </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="仿宋"/>
-        <family val="3"/>
-        <charset val="134"/>
-      </rPr>
-      <t>端羟基聚丁二烯）</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>NTO/HTPB</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="仿宋"/>
-        <family val="3"/>
-        <charset val="134"/>
-      </rPr>
-      <t>（</t>
+      <t xml:space="preserve">3 - </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="仿宋"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>硝基</t>
     </r>
     <r>
       <rPr>
@@ -760,17 +755,17 @@
         <rFont val="Times New Roman"/>
         <family val="1"/>
       </rPr>
-      <t xml:space="preserve">3 - </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="仿宋"/>
-        <family val="3"/>
-        <charset val="134"/>
-      </rPr>
-      <t>硝基</t>
+      <t xml:space="preserve"> - 1,2,4 - </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="仿宋"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>三唑</t>
     </r>
     <r>
       <rPr>
@@ -779,17 +774,17 @@
         <rFont val="Times New Roman"/>
         <family val="1"/>
       </rPr>
-      <t xml:space="preserve"> - 1,2,4 - </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="仿宋"/>
-        <family val="3"/>
-        <charset val="134"/>
-      </rPr>
-      <t>三唑</t>
+      <t xml:space="preserve"> - 5 - </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="仿宋"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>酮</t>
     </r>
     <r>
       <rPr>
@@ -798,47 +793,53 @@
         <rFont val="Times New Roman"/>
         <family val="1"/>
       </rPr>
-      <t xml:space="preserve"> - 5 - </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="仿宋"/>
-        <family val="3"/>
-        <charset val="134"/>
-      </rPr>
-      <t>酮</t>
-    </r>
-    <r>
-      <rPr>
+      <t xml:space="preserve"> / </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="仿宋"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>端羟基聚丁二烯）</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="仿宋"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>杨氏模量</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
         <sz val="12"/>
         <color theme="1"/>
         <rFont val="Times New Roman"/>
         <family val="1"/>
       </rPr>
-      <t xml:space="preserve"> / </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="仿宋"/>
-        <family val="3"/>
-        <charset val="134"/>
-      </rPr>
-      <t>端羟基聚丁二烯）</t>
-    </r>
+      <t>[GPa]</t>
+    </r>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="1">
+  <numFmts count="2">
     <numFmt numFmtId="176" formatCode="0;[Red]0"/>
+    <numFmt numFmtId="177" formatCode="0.00_);[Red]\(0.00\)"/>
   </numFmts>
-  <fonts count="7">
+  <fonts count="8" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <name val="Calibri"/>
@@ -884,6 +885,14 @@
       <family val="3"/>
       <charset val="134"/>
     </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Times New Roman"/>
+      <family val="3"/>
+      <charset val="134"/>
+    </font>
   </fonts>
   <fills count="3">
     <fill>
@@ -926,7 +935,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -956,6 +965,15 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="176" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1263,9 +1281,12 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:W16"/>
-  <sheetFormatPr defaultRowHeight="14.6"/>
+  <sheetFormatPr defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
+  <cols>
+    <col min="6" max="6" width="18" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:23" ht="15">
+    <row r="1" spans="1:23" ht="15" x14ac:dyDescent="0.4">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1281,70 +1302,70 @@
       <c r="E1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="2" t="s">
+      <c r="F1" s="11" t="s">
+        <v>40</v>
+      </c>
+      <c r="G1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="H1" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="2" t="s">
+      <c r="I1" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="3" t="s">
+      <c r="J1" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="K1" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="2" t="s">
+      <c r="L1" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="1" t="s">
+      <c r="M1" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="1" t="s">
+      <c r="N1" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="N1" s="1" t="s">
+      <c r="O1" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="O1" s="1" t="s">
+      <c r="P1" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="P1" s="1" t="s">
+      <c r="Q1" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="Q1" s="2" t="s">
+      <c r="R1" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="R1" s="1" t="s">
+      <c r="S1" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="S1" s="1" t="s">
+      <c r="T1" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="T1" s="1" t="s">
+      <c r="U1" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="U1" s="1" t="s">
+      <c r="V1" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="V1" s="1" t="s">
+      <c r="W1" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="W1" s="1" t="s">
-        <v>22</v>
-      </c>
     </row>
-    <row r="2" spans="1:23" ht="15.45">
+    <row r="2" spans="1:23" ht="15.45" x14ac:dyDescent="0.4">
       <c r="A2" s="4">
         <v>1</v>
       </c>
       <c r="B2" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="C2" s="5" t="s">
         <v>23</v>
-      </c>
-      <c r="C2" s="5" t="s">
-        <v>24</v>
       </c>
       <c r="D2" s="4">
         <v>1750</v>
@@ -1352,8 +1373,8 @@
       <c r="E2" s="6">
         <v>6.3E-5</v>
       </c>
-      <c r="F2" s="6">
-        <v>10000000000</v>
+      <c r="F2" s="12">
+        <v>10</v>
       </c>
       <c r="G2" s="4">
         <v>0.495</v>
@@ -1407,15 +1428,15 @@
         <v>9.6</v>
       </c>
     </row>
-    <row r="3" spans="1:23" ht="30">
+    <row r="3" spans="1:23" ht="30" x14ac:dyDescent="0.4">
       <c r="A3" s="4">
         <v>2</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C3" s="5" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D3" s="5">
         <v>1700</v>
@@ -1423,8 +1444,8 @@
       <c r="E3" s="8">
         <v>6.2000000000000003E-5</v>
       </c>
-      <c r="F3" s="8">
-        <v>11000000000</v>
+      <c r="F3" s="13">
+        <v>11</v>
       </c>
       <c r="G3" s="5">
         <v>0.46</v>
@@ -1478,15 +1499,15 @@
         <v>2.1</v>
       </c>
     </row>
-    <row r="4" spans="1:23" ht="30">
+    <row r="4" spans="1:23" ht="30" x14ac:dyDescent="0.4">
       <c r="A4" s="4">
         <v>3</v>
       </c>
       <c r="B4" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="C4" s="5" t="s">
         <v>26</v>
-      </c>
-      <c r="C4" s="5" t="s">
-        <v>27</v>
       </c>
       <c r="D4" s="5">
         <v>1780</v>
@@ -1494,8 +1515,8 @@
       <c r="E4" s="8">
         <v>6.3E-5</v>
       </c>
-      <c r="F4" s="8">
-        <v>11500000000</v>
+      <c r="F4" s="13">
+        <v>11.5</v>
       </c>
       <c r="G4" s="5">
         <v>0.47</v>
@@ -1549,15 +1570,15 @@
         <v>2.2000000000000002</v>
       </c>
     </row>
-    <row r="5" spans="1:23" ht="15.45">
+    <row r="5" spans="1:23" ht="15.45" x14ac:dyDescent="0.4">
       <c r="A5" s="4">
         <v>4</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D5" s="5">
         <v>1650</v>
@@ -1565,8 +1586,8 @@
       <c r="E5" s="8">
         <v>6.0000000000000002E-5</v>
       </c>
-      <c r="F5" s="8">
-        <v>10500000000</v>
+      <c r="F5" s="13">
+        <v>10.5</v>
       </c>
       <c r="G5" s="5">
         <v>0.45</v>
@@ -1620,15 +1641,15 @@
         <v>2</v>
       </c>
     </row>
-    <row r="6" spans="1:23" ht="15.45">
+    <row r="6" spans="1:23" ht="15.45" x14ac:dyDescent="0.4">
       <c r="A6" s="4">
         <v>5</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C6" s="5" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D6" s="5">
         <v>1820</v>
@@ -1636,8 +1657,8 @@
       <c r="E6" s="8">
         <v>6.3999999999999997E-5</v>
       </c>
-      <c r="F6" s="8">
-        <v>12000000000</v>
+      <c r="F6" s="13">
+        <v>12</v>
       </c>
       <c r="G6" s="5">
         <v>0.48</v>
@@ -1691,15 +1712,15 @@
         <v>2.2999999999999998</v>
       </c>
     </row>
-    <row r="7" spans="1:23" ht="92.15">
+    <row r="7" spans="1:23" ht="92.15" x14ac:dyDescent="0.4">
       <c r="A7" s="4">
         <v>6</v>
       </c>
       <c r="B7" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="C7" s="9" t="s">
         <v>30</v>
-      </c>
-      <c r="C7" s="9" t="s">
-        <v>31</v>
       </c>
       <c r="D7" s="5">
         <v>1750</v>
@@ -1707,8 +1728,8 @@
       <c r="E7" s="8">
         <v>6.0000000000000002E-5</v>
       </c>
-      <c r="F7" s="8">
-        <v>12000000000</v>
+      <c r="F7" s="13">
+        <v>12</v>
       </c>
       <c r="G7" s="5">
         <v>0.45</v>
@@ -1762,15 +1783,15 @@
         <v>9</v>
       </c>
     </row>
-    <row r="8" spans="1:23" ht="108">
+    <row r="8" spans="1:23" ht="108" x14ac:dyDescent="0.4">
       <c r="A8" s="4">
         <v>7</v>
       </c>
       <c r="B8" s="5" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C8" s="5" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D8" s="5">
         <v>1850</v>
@@ -1778,8 +1799,8 @@
       <c r="E8" s="8">
         <v>5.8E-5</v>
       </c>
-      <c r="F8" s="8">
-        <v>13000000000</v>
+      <c r="F8" s="13">
+        <v>13</v>
       </c>
       <c r="G8" s="5">
         <v>0.46</v>
@@ -1833,15 +1854,15 @@
         <v>9.1999999999999993</v>
       </c>
     </row>
-    <row r="9" spans="1:23" ht="61.3">
+    <row r="9" spans="1:23" ht="61.3" x14ac:dyDescent="0.4">
       <c r="A9" s="4">
         <v>8</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C9" s="9" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D9" s="5">
         <v>1600</v>
@@ -1849,8 +1870,8 @@
       <c r="E9" s="8">
         <v>6.9999999999999994E-5</v>
       </c>
-      <c r="F9" s="8">
-        <v>10000000000</v>
+      <c r="F9" s="13">
+        <v>10</v>
       </c>
       <c r="G9" s="5">
         <v>0.48</v>
@@ -1904,15 +1925,15 @@
         <v>8.8000000000000007</v>
       </c>
     </row>
-    <row r="10" spans="1:23" ht="136.75">
+    <row r="10" spans="1:23" ht="136.75" x14ac:dyDescent="0.4">
       <c r="A10" s="4">
         <v>9</v>
       </c>
       <c r="B10" s="5" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C10" s="9" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D10" s="5">
         <v>1900</v>
@@ -1920,8 +1941,8 @@
       <c r="E10" s="8">
         <v>5.5000000000000002E-5</v>
       </c>
-      <c r="F10" s="8">
-        <v>14000000000</v>
+      <c r="F10" s="13">
+        <v>14</v>
       </c>
       <c r="G10" s="5">
         <v>0.44</v>
@@ -1975,15 +1996,15 @@
         <v>9.5</v>
       </c>
     </row>
-    <row r="11" spans="1:23" ht="92.15">
+    <row r="11" spans="1:23" ht="92.15" x14ac:dyDescent="0.4">
       <c r="A11" s="4">
         <v>10</v>
       </c>
       <c r="B11" s="5" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C11" s="9" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D11" s="5">
         <v>1650</v>
@@ -1991,8 +2012,8 @@
       <c r="E11" s="8">
         <v>6.2000000000000003E-5</v>
       </c>
-      <c r="F11" s="8">
-        <v>11000000000</v>
+      <c r="F11" s="13">
+        <v>11</v>
       </c>
       <c r="G11" s="5">
         <v>0.47</v>
@@ -2046,15 +2067,15 @@
         <v>9</v>
       </c>
     </row>
-    <row r="12" spans="1:23" ht="92.15">
+    <row r="12" spans="1:23" ht="92.15" x14ac:dyDescent="0.4">
       <c r="A12" s="4">
         <v>11</v>
       </c>
       <c r="B12" s="5" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C12" s="9" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D12" s="5">
         <v>1880</v>
@@ -2062,8 +2083,8 @@
       <c r="E12" s="8">
         <v>5.5999999999999999E-5</v>
       </c>
-      <c r="F12" s="8">
-        <v>13500000000</v>
+      <c r="F12" s="13">
+        <v>13.5</v>
       </c>
       <c r="G12" s="5">
         <v>0.45</v>
@@ -2117,15 +2138,15 @@
         <v>9.3000000000000007</v>
       </c>
     </row>
-    <row r="13" spans="1:23" ht="76.3">
+    <row r="13" spans="1:23" ht="76.3" x14ac:dyDescent="0.4">
       <c r="A13" s="4">
         <v>12</v>
       </c>
       <c r="B13" s="5" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C13" s="9" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D13" s="5">
         <v>1800</v>
@@ -2133,8 +2154,8 @@
       <c r="E13" s="8">
         <v>5.8999999999999998E-5</v>
       </c>
-      <c r="F13" s="8">
-        <v>12500000000</v>
+      <c r="F13" s="13">
+        <v>12.5</v>
       </c>
       <c r="G13" s="5">
         <v>0.46</v>
@@ -2188,15 +2209,15 @@
         <v>9.1</v>
       </c>
     </row>
-    <row r="14" spans="1:23" ht="139.30000000000001">
+    <row r="14" spans="1:23" ht="139.30000000000001" x14ac:dyDescent="0.4">
       <c r="A14" s="4">
         <v>13</v>
       </c>
       <c r="B14" s="5" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C14" s="9" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D14" s="5">
         <v>1780</v>
@@ -2204,8 +2225,8 @@
       <c r="E14" s="8">
         <v>5.7000000000000003E-5</v>
       </c>
-      <c r="F14" s="8">
-        <v>13200000000</v>
+      <c r="F14" s="13">
+        <v>13.2</v>
       </c>
       <c r="G14" s="5">
         <v>0.45</v>
@@ -2259,15 +2280,15 @@
         <v>9.1999999999999993</v>
       </c>
     </row>
-    <row r="15" spans="1:23" ht="122.15">
+    <row r="15" spans="1:23" ht="122.15" x14ac:dyDescent="0.4">
       <c r="A15" s="4">
         <v>14</v>
       </c>
       <c r="B15" s="5" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C15" s="9" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D15" s="5">
         <v>1680</v>
@@ -2275,8 +2296,8 @@
       <c r="E15" s="8">
         <v>6.4999999999999994E-5</v>
       </c>
-      <c r="F15" s="8">
-        <v>10500000000</v>
+      <c r="F15" s="13">
+        <v>10.5</v>
       </c>
       <c r="G15" s="5">
         <v>0.47</v>
@@ -2330,15 +2351,15 @@
         <v>8.9</v>
       </c>
     </row>
-    <row r="16" spans="1:23" ht="124.75">
+    <row r="16" spans="1:23" ht="124.75" x14ac:dyDescent="0.4">
       <c r="A16" s="4">
         <v>15</v>
       </c>
       <c r="B16" s="5" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C16" s="9" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D16" s="5">
         <v>1720</v>
@@ -2346,8 +2367,8 @@
       <c r="E16" s="8">
         <v>6.0999999999999999E-5</v>
       </c>
-      <c r="F16" s="8">
-        <v>11500000000</v>
+      <c r="F16" s="13">
+        <v>11.5</v>
       </c>
       <c r="G16" s="5">
         <v>0.46</v>

--- a/mainWidget/mainWidget/src/database/推进剂材料.xlsx
+++ b/mainWidget/mainWidget/src/database/推进剂材料.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\VSProject\git\GFApp\mainWidget\mainWidget\src\database\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C0751E53-EBC6-42F6-BEDC-AB82A7C43E2C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8DCEC8BF-5585-49CA-A13A-13B3593F4631}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-103" yWindow="-103" windowWidth="22149" windowHeight="13320" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="53" uniqueCount="41">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="307" uniqueCount="171">
   <si>
     <r>
       <rPr>
@@ -829,15 +829,534 @@
       <t>[GPa]</t>
     </r>
     <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>10</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>11</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>11.5</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>10.5</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>12</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0.5</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0.45</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0.48</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0.42</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0.6</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0.4</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0.65</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0.55</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0.62</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0.58</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0.53</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>13</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>14</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>13.5</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>12.5</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>13.2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0.495</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0.46</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0.47</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0.44</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>70</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>250</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>260</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>240</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>8</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>270</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>300</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>280</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>180</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>7</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>220</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>15</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>9</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>230</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>200</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1256.1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1280</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1300</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1330</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1450</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1260</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1230</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1320</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1200</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1250</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1400</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0.667</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0.66</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0.67</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0.68</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0.63</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0.64</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>6.1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0.31</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1.35</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2.05</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>9.1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>9.2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2.1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1.4</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>820</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1.1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0.32</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>6.2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0.11</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0.09</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0.29</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0.95</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1.25</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>8.9</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1.3</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>800</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0.3</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0.1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0.12</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>6.3</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>6</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>6.5</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0.35</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0.33</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1.2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>830</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1.5</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2.2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>9.3</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>9.5</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0.111</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0.333</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0.34</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>5.8</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0.28</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0.9</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>780</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1.9</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>8.8</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2.3</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>9.6</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1.8</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1.6</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>790</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>6.8</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0.000063</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0.000062</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0.00006</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0.000064</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0.000058</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0.00007</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0.000055</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0.000056</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0.000061</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0.000065</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0.000057</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0.000059</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>740000000000</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>750000000000</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>730000000000</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>710000000000</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>690000000000</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>680000000000</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>780000000000</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>700000000000</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>760000000000</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>720000000000</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="2">
+  <numFmts count="1">
     <numFmt numFmtId="176" formatCode="0;[Red]0"/>
-    <numFmt numFmtId="177" formatCode="0.00_);[Red]\(0.00\)"/>
   </numFmts>
   <fonts count="8" x14ac:knownFonts="1">
     <font>
@@ -935,7 +1454,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -952,30 +1471,25 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="11" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="11" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="176" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="177" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="177" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -1283,7 +1797,10 @@
   <dimension ref="A1:W16"/>
   <sheetFormatPr defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
   <cols>
+    <col min="5" max="5" width="9.23046875" style="12"/>
     <col min="6" max="6" width="18" customWidth="1"/>
+    <col min="12" max="12" width="12.07421875" style="12" customWidth="1"/>
+    <col min="13" max="23" width="9.23046875" style="12"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:23" ht="15" x14ac:dyDescent="0.4">
@@ -1299,10 +1816,10 @@
       <c r="D1" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" s="10" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="11" t="s">
+      <c r="F1" s="7" t="s">
         <v>40</v>
       </c>
       <c r="G1" s="1" t="s">
@@ -1320,40 +1837,40 @@
       <c r="K1" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="L1" s="1" t="s">
+      <c r="L1" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="M1" s="1" t="s">
+      <c r="M1" s="10" t="s">
         <v>11</v>
       </c>
-      <c r="N1" s="1" t="s">
+      <c r="N1" s="10" t="s">
         <v>12</v>
       </c>
-      <c r="O1" s="1" t="s">
+      <c r="O1" s="10" t="s">
         <v>13</v>
       </c>
-      <c r="P1" s="1" t="s">
+      <c r="P1" s="10" t="s">
         <v>14</v>
       </c>
-      <c r="Q1" s="2" t="s">
+      <c r="Q1" s="11" t="s">
         <v>15</v>
       </c>
-      <c r="R1" s="1" t="s">
+      <c r="R1" s="10" t="s">
         <v>16</v>
       </c>
-      <c r="S1" s="1" t="s">
+      <c r="S1" s="10" t="s">
         <v>17</v>
       </c>
-      <c r="T1" s="1" t="s">
+      <c r="T1" s="10" t="s">
         <v>18</v>
       </c>
-      <c r="U1" s="1" t="s">
+      <c r="U1" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="V1" s="1" t="s">
+      <c r="V1" s="10" t="s">
         <v>20</v>
       </c>
-      <c r="W1" s="1" t="s">
+      <c r="W1" s="10" t="s">
         <v>21</v>
       </c>
     </row>
@@ -1370,62 +1887,62 @@
       <c r="D2" s="4">
         <v>1750</v>
       </c>
-      <c r="E2" s="6">
-        <v>6.3E-5</v>
-      </c>
-      <c r="F2" s="12">
-        <v>10</v>
-      </c>
-      <c r="G2" s="4">
-        <v>0.495</v>
-      </c>
-      <c r="H2" s="4">
-        <v>70</v>
-      </c>
-      <c r="I2" s="7">
-        <v>10</v>
-      </c>
-      <c r="J2" s="4">
-        <v>0.5</v>
-      </c>
-      <c r="K2" s="4">
-        <v>1256.0999999999999</v>
-      </c>
-      <c r="L2" s="6">
-        <v>740000000000</v>
-      </c>
-      <c r="M2" s="4">
+      <c r="E2" s="8" t="s">
+        <v>149</v>
+      </c>
+      <c r="F2" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="G2" s="8" t="s">
+        <v>62</v>
+      </c>
+      <c r="H2" s="8" t="s">
+        <v>66</v>
+      </c>
+      <c r="I2" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="J2" s="8" t="s">
+        <v>46</v>
+      </c>
+      <c r="K2" s="8" t="s">
+        <v>81</v>
+      </c>
+      <c r="L2" s="8" t="s">
+        <v>161</v>
+      </c>
+      <c r="M2" s="8">
         <v>0</v>
       </c>
-      <c r="N2" s="4">
-        <v>0.66700000000000004</v>
-      </c>
-      <c r="O2" s="4">
-        <v>0.66700000000000004</v>
-      </c>
-      <c r="P2" s="4">
-        <v>0.111</v>
-      </c>
-      <c r="Q2" s="4">
-        <v>7</v>
-      </c>
-      <c r="R2" s="4">
-        <v>0.33300000000000002</v>
-      </c>
-      <c r="S2" s="4">
-        <v>1</v>
-      </c>
-      <c r="T2" s="4">
-        <v>800</v>
-      </c>
-      <c r="U2" s="4">
-        <v>1.5</v>
-      </c>
-      <c r="V2" s="4">
-        <v>2</v>
-      </c>
-      <c r="W2" s="4">
-        <v>9.6</v>
+      <c r="N2" s="8" t="s">
+        <v>92</v>
+      </c>
+      <c r="O2" s="8" t="s">
+        <v>92</v>
+      </c>
+      <c r="P2" s="8" t="s">
+        <v>134</v>
+      </c>
+      <c r="Q2" s="8" t="s">
+        <v>75</v>
+      </c>
+      <c r="R2" s="8" t="s">
+        <v>135</v>
+      </c>
+      <c r="S2" s="8" t="s">
+        <v>119</v>
+      </c>
+      <c r="T2" s="8" t="s">
+        <v>118</v>
+      </c>
+      <c r="U2" s="8" t="s">
+        <v>130</v>
+      </c>
+      <c r="V2" s="8" t="s">
+        <v>115</v>
+      </c>
+      <c r="W2" s="8" t="s">
+        <v>144</v>
       </c>
     </row>
     <row r="3" spans="1:23" ht="30" x14ac:dyDescent="0.4">
@@ -1441,62 +1958,62 @@
       <c r="D3" s="5">
         <v>1700</v>
       </c>
-      <c r="E3" s="8">
-        <v>6.2000000000000003E-5</v>
-      </c>
-      <c r="F3" s="13">
-        <v>11</v>
-      </c>
-      <c r="G3" s="5">
-        <v>0.46</v>
-      </c>
-      <c r="H3" s="5">
-        <v>250</v>
-      </c>
-      <c r="I3" s="5">
+      <c r="E3" s="9" t="s">
+        <v>150</v>
+      </c>
+      <c r="F3" s="9" t="s">
+        <v>42</v>
+      </c>
+      <c r="G3" s="9" t="s">
+        <v>63</v>
+      </c>
+      <c r="H3" s="9" t="s">
+        <v>67</v>
+      </c>
+      <c r="I3" s="9">
         <v>9</v>
       </c>
-      <c r="J3" s="5">
-        <v>0.45</v>
-      </c>
-      <c r="K3" s="5">
-        <v>1280</v>
-      </c>
-      <c r="L3" s="6">
-        <v>750000000000</v>
-      </c>
-      <c r="M3" s="5">
+      <c r="J3" s="9" t="s">
+        <v>47</v>
+      </c>
+      <c r="K3" s="9" t="s">
+        <v>82</v>
+      </c>
+      <c r="L3" s="8" t="s">
+        <v>162</v>
+      </c>
+      <c r="M3" s="9">
         <v>0</v>
       </c>
-      <c r="N3" s="5">
-        <v>0.66</v>
-      </c>
-      <c r="O3" s="5">
-        <v>0.66</v>
-      </c>
-      <c r="P3" s="5">
-        <v>0.11</v>
-      </c>
-      <c r="Q3" s="5">
-        <v>6.5</v>
-      </c>
-      <c r="R3" s="5">
-        <v>0.34</v>
-      </c>
-      <c r="S3" s="5">
-        <v>1</v>
-      </c>
-      <c r="T3" s="5">
-        <v>800</v>
-      </c>
-      <c r="U3" s="5">
-        <v>1.4</v>
-      </c>
-      <c r="V3" s="5">
-        <v>1.9</v>
-      </c>
-      <c r="W3" s="5">
-        <v>2.1</v>
+      <c r="N3" s="9" t="s">
+        <v>93</v>
+      </c>
+      <c r="O3" s="9" t="s">
+        <v>93</v>
+      </c>
+      <c r="P3" s="9" t="s">
+        <v>110</v>
+      </c>
+      <c r="Q3" s="9" t="s">
+        <v>125</v>
+      </c>
+      <c r="R3" s="9" t="s">
+        <v>136</v>
+      </c>
+      <c r="S3" s="9" t="s">
+        <v>119</v>
+      </c>
+      <c r="T3" s="9" t="s">
+        <v>118</v>
+      </c>
+      <c r="U3" s="9" t="s">
+        <v>105</v>
+      </c>
+      <c r="V3" s="9" t="s">
+        <v>141</v>
+      </c>
+      <c r="W3" s="9" t="s">
+        <v>104</v>
       </c>
     </row>
     <row r="4" spans="1:23" ht="30" x14ac:dyDescent="0.4">
@@ -1512,62 +2029,62 @@
       <c r="D4" s="5">
         <v>1780</v>
       </c>
-      <c r="E4" s="8">
-        <v>6.3E-5</v>
-      </c>
-      <c r="F4" s="13">
-        <v>11.5</v>
-      </c>
-      <c r="G4" s="5">
-        <v>0.47</v>
-      </c>
-      <c r="H4" s="5">
-        <v>260</v>
-      </c>
-      <c r="I4" s="5">
-        <v>10</v>
-      </c>
-      <c r="J4" s="5">
-        <v>0.48</v>
-      </c>
-      <c r="K4" s="5">
-        <v>1300</v>
-      </c>
-      <c r="L4" s="6">
-        <v>730000000000</v>
-      </c>
-      <c r="M4" s="5">
+      <c r="E4" s="9" t="s">
+        <v>149</v>
+      </c>
+      <c r="F4" s="9" t="s">
+        <v>43</v>
+      </c>
+      <c r="G4" s="9" t="s">
+        <v>64</v>
+      </c>
+      <c r="H4" s="9" t="s">
+        <v>68</v>
+      </c>
+      <c r="I4" s="9" t="s">
+        <v>41</v>
+      </c>
+      <c r="J4" s="9" t="s">
+        <v>48</v>
+      </c>
+      <c r="K4" s="9" t="s">
+        <v>83</v>
+      </c>
+      <c r="L4" s="8" t="s">
+        <v>163</v>
+      </c>
+      <c r="M4" s="9">
         <v>0</v>
       </c>
-      <c r="N4" s="5">
+      <c r="N4" s="9" t="s">
+        <v>94</v>
+      </c>
+      <c r="O4" s="9">
         <v>0.67</v>
       </c>
-      <c r="O4" s="5">
-        <v>0.67</v>
-      </c>
-      <c r="P4" s="5">
-        <v>0.12</v>
-      </c>
-      <c r="Q4" s="5">
-        <v>6.8</v>
-      </c>
-      <c r="R4" s="5">
-        <v>0.35</v>
-      </c>
-      <c r="S4" s="5">
-        <v>1.1000000000000001</v>
-      </c>
-      <c r="T4" s="5">
-        <v>820</v>
-      </c>
-      <c r="U4" s="5">
-        <v>1.5</v>
-      </c>
-      <c r="V4" s="5">
-        <v>2</v>
-      </c>
-      <c r="W4" s="5">
-        <v>2.2000000000000002</v>
+      <c r="P4" s="9" t="s">
+        <v>122</v>
+      </c>
+      <c r="Q4" s="9" t="s">
+        <v>148</v>
+      </c>
+      <c r="R4" s="9" t="s">
+        <v>126</v>
+      </c>
+      <c r="S4" s="9" t="s">
+        <v>107</v>
+      </c>
+      <c r="T4" s="9" t="s">
+        <v>106</v>
+      </c>
+      <c r="U4" s="9" t="s">
+        <v>130</v>
+      </c>
+      <c r="V4" s="9" t="s">
+        <v>115</v>
+      </c>
+      <c r="W4" s="9" t="s">
+        <v>131</v>
       </c>
     </row>
     <row r="5" spans="1:23" ht="15.45" x14ac:dyDescent="0.4">
@@ -1583,65 +2100,65 @@
       <c r="D5" s="5">
         <v>1650</v>
       </c>
-      <c r="E5" s="8">
-        <v>6.0000000000000002E-5</v>
-      </c>
-      <c r="F5" s="13">
-        <v>10.5</v>
-      </c>
-      <c r="G5" s="5">
-        <v>0.45</v>
-      </c>
-      <c r="H5" s="5">
-        <v>240</v>
-      </c>
-      <c r="I5" s="5">
-        <v>8</v>
-      </c>
-      <c r="J5" s="5">
-        <v>0.42</v>
-      </c>
-      <c r="K5" s="5">
-        <v>1250</v>
-      </c>
-      <c r="L5" s="6">
-        <v>750000000000</v>
-      </c>
-      <c r="M5" s="5">
+      <c r="E5" s="9" t="s">
+        <v>151</v>
+      </c>
+      <c r="F5" s="9" t="s">
+        <v>44</v>
+      </c>
+      <c r="G5" s="9" t="s">
+        <v>47</v>
+      </c>
+      <c r="H5" s="9" t="s">
+        <v>69</v>
+      </c>
+      <c r="I5" s="9" t="s">
+        <v>70</v>
+      </c>
+      <c r="J5" s="9" t="s">
+        <v>49</v>
+      </c>
+      <c r="K5" s="9" t="s">
+        <v>90</v>
+      </c>
+      <c r="L5" s="8" t="s">
+        <v>162</v>
+      </c>
+      <c r="M5" s="9">
         <v>0</v>
       </c>
-      <c r="N5" s="5">
-        <v>0.65</v>
-      </c>
-      <c r="O5" s="5">
-        <v>0.65</v>
-      </c>
-      <c r="P5" s="5">
-        <v>0.1</v>
-      </c>
-      <c r="Q5" s="5">
-        <v>6.2</v>
-      </c>
-      <c r="R5" s="5">
-        <v>0.32</v>
-      </c>
-      <c r="S5" s="5">
-        <v>1</v>
-      </c>
-      <c r="T5" s="5">
-        <v>790</v>
-      </c>
-      <c r="U5" s="5">
-        <v>1.3</v>
-      </c>
-      <c r="V5" s="5">
-        <v>1.8</v>
-      </c>
-      <c r="W5" s="5">
-        <v>2</v>
+      <c r="N5" s="9" t="s">
+        <v>52</v>
+      </c>
+      <c r="O5" s="9" t="s">
+        <v>52</v>
+      </c>
+      <c r="P5" s="9" t="s">
+        <v>121</v>
+      </c>
+      <c r="Q5" s="9" t="s">
+        <v>109</v>
+      </c>
+      <c r="R5" s="9" t="s">
+        <v>108</v>
+      </c>
+      <c r="S5" s="9" t="s">
+        <v>119</v>
+      </c>
+      <c r="T5" s="9" t="s">
+        <v>147</v>
+      </c>
+      <c r="U5" s="9" t="s">
+        <v>117</v>
+      </c>
+      <c r="V5" s="9" t="s">
+        <v>145</v>
+      </c>
+      <c r="W5" s="9" t="s">
+        <v>115</v>
       </c>
     </row>
-    <row r="6" spans="1:23" ht="15.45" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:23" ht="30.9" x14ac:dyDescent="0.4">
       <c r="A6" s="4">
         <v>5</v>
       </c>
@@ -1654,62 +2171,62 @@
       <c r="D6" s="5">
         <v>1820</v>
       </c>
-      <c r="E6" s="8">
-        <v>6.3999999999999997E-5</v>
-      </c>
-      <c r="F6" s="13">
-        <v>12</v>
-      </c>
-      <c r="G6" s="5">
-        <v>0.48</v>
-      </c>
-      <c r="H6" s="5">
-        <v>270</v>
-      </c>
-      <c r="I6" s="5">
-        <v>11</v>
-      </c>
-      <c r="J6" s="5">
-        <v>0.5</v>
-      </c>
-      <c r="K6" s="5">
-        <v>1320</v>
-      </c>
-      <c r="L6" s="8">
-        <v>780000000000</v>
-      </c>
-      <c r="M6" s="5">
+      <c r="E6" s="9" t="s">
+        <v>152</v>
+      </c>
+      <c r="F6" s="9" t="s">
+        <v>45</v>
+      </c>
+      <c r="G6" s="9" t="s">
+        <v>48</v>
+      </c>
+      <c r="H6" s="9" t="s">
+        <v>71</v>
+      </c>
+      <c r="I6" s="9" t="s">
+        <v>42</v>
+      </c>
+      <c r="J6" s="9" t="s">
+        <v>46</v>
+      </c>
+      <c r="K6" s="9" t="s">
+        <v>88</v>
+      </c>
+      <c r="L6" s="9" t="s">
+        <v>167</v>
+      </c>
+      <c r="M6" s="9">
         <v>0</v>
       </c>
-      <c r="N6" s="5">
+      <c r="N6" s="9" t="s">
+        <v>95</v>
+      </c>
+      <c r="O6" s="9">
         <v>0.68</v>
       </c>
-      <c r="O6" s="5">
-        <v>0.68</v>
-      </c>
-      <c r="P6" s="5">
+      <c r="P6" s="9">
         <v>0.13</v>
       </c>
-      <c r="Q6" s="5">
+      <c r="Q6" s="9">
         <v>7</v>
       </c>
-      <c r="R6" s="5">
+      <c r="R6" s="9">
         <v>0.36</v>
       </c>
-      <c r="S6" s="5">
+      <c r="S6" s="9">
         <v>1.2</v>
       </c>
-      <c r="T6" s="5">
+      <c r="T6" s="9">
         <v>830</v>
       </c>
-      <c r="U6" s="5">
-        <v>1.6</v>
-      </c>
-      <c r="V6" s="5">
-        <v>2.1</v>
-      </c>
-      <c r="W6" s="5">
-        <v>2.2999999999999998</v>
+      <c r="U6" s="9" t="s">
+        <v>146</v>
+      </c>
+      <c r="V6" s="9" t="s">
+        <v>104</v>
+      </c>
+      <c r="W6" s="9" t="s">
+        <v>143</v>
       </c>
     </row>
     <row r="7" spans="1:23" ht="92.15" x14ac:dyDescent="0.4">
@@ -1719,68 +2236,68 @@
       <c r="B7" s="5" t="s">
         <v>29</v>
       </c>
-      <c r="C7" s="9" t="s">
+      <c r="C7" s="6" t="s">
         <v>30</v>
       </c>
       <c r="D7" s="5">
         <v>1750</v>
       </c>
-      <c r="E7" s="8">
-        <v>6.0000000000000002E-5</v>
-      </c>
-      <c r="F7" s="13">
-        <v>12</v>
-      </c>
-      <c r="G7" s="5">
-        <v>0.45</v>
-      </c>
-      <c r="H7" s="5">
-        <v>300</v>
-      </c>
-      <c r="I7" s="10">
-        <v>10</v>
-      </c>
-      <c r="J7" s="5">
-        <v>0.5</v>
-      </c>
-      <c r="K7" s="5">
-        <v>1300</v>
-      </c>
-      <c r="L7" s="8">
-        <v>720000000000</v>
-      </c>
-      <c r="M7" s="4">
+      <c r="E7" s="9" t="s">
+        <v>151</v>
+      </c>
+      <c r="F7" s="9" t="s">
+        <v>45</v>
+      </c>
+      <c r="G7" s="9" t="s">
+        <v>47</v>
+      </c>
+      <c r="H7" s="9" t="s">
+        <v>72</v>
+      </c>
+      <c r="I7" s="9" t="s">
+        <v>41</v>
+      </c>
+      <c r="J7" s="9" t="s">
+        <v>46</v>
+      </c>
+      <c r="K7" s="9" t="s">
+        <v>83</v>
+      </c>
+      <c r="L7" s="9" t="s">
+        <v>170</v>
+      </c>
+      <c r="M7" s="8">
         <v>0</v>
       </c>
-      <c r="N7" s="5">
-        <v>0.65</v>
-      </c>
-      <c r="O7" s="5">
-        <v>0.65</v>
-      </c>
-      <c r="P7" s="5">
-        <v>0.1</v>
-      </c>
-      <c r="Q7" s="5">
-        <v>6</v>
-      </c>
-      <c r="R7" s="5">
-        <v>0.3</v>
-      </c>
-      <c r="S7" s="5">
-        <v>1</v>
-      </c>
-      <c r="T7" s="5">
-        <v>800</v>
-      </c>
-      <c r="U7" s="5">
-        <v>1.3</v>
-      </c>
-      <c r="V7" s="5">
-        <v>2</v>
-      </c>
-      <c r="W7" s="5">
-        <v>9</v>
+      <c r="N7" s="9" t="s">
+        <v>52</v>
+      </c>
+      <c r="O7" s="9" t="s">
+        <v>52</v>
+      </c>
+      <c r="P7" s="9" t="s">
+        <v>121</v>
+      </c>
+      <c r="Q7" s="9" t="s">
+        <v>124</v>
+      </c>
+      <c r="R7" s="9" t="s">
+        <v>120</v>
+      </c>
+      <c r="S7" s="9" t="s">
+        <v>119</v>
+      </c>
+      <c r="T7" s="9" t="s">
+        <v>118</v>
+      </c>
+      <c r="U7" s="9" t="s">
+        <v>117</v>
+      </c>
+      <c r="V7" s="9" t="s">
+        <v>115</v>
+      </c>
+      <c r="W7" s="9" t="s">
+        <v>78</v>
       </c>
     </row>
     <row r="8" spans="1:23" ht="108" x14ac:dyDescent="0.4">
@@ -1796,62 +2313,62 @@
       <c r="D8" s="5">
         <v>1850</v>
       </c>
-      <c r="E8" s="8">
-        <v>5.8E-5</v>
-      </c>
-      <c r="F8" s="13">
-        <v>13</v>
-      </c>
-      <c r="G8" s="5">
-        <v>0.46</v>
-      </c>
-      <c r="H8" s="5">
-        <v>280</v>
-      </c>
-      <c r="I8" s="10">
-        <v>12</v>
-      </c>
-      <c r="J8" s="5">
-        <v>0.6</v>
-      </c>
-      <c r="K8" s="5">
-        <v>1250</v>
-      </c>
-      <c r="L8" s="8">
-        <v>750000000000</v>
-      </c>
-      <c r="M8" s="4">
+      <c r="E8" s="9" t="s">
+        <v>153</v>
+      </c>
+      <c r="F8" s="9" t="s">
+        <v>57</v>
+      </c>
+      <c r="G8" s="9" t="s">
+        <v>63</v>
+      </c>
+      <c r="H8" s="9" t="s">
+        <v>73</v>
+      </c>
+      <c r="I8" s="9" t="s">
+        <v>45</v>
+      </c>
+      <c r="J8" s="9" t="s">
+        <v>50</v>
+      </c>
+      <c r="K8" s="9" t="s">
+        <v>90</v>
+      </c>
+      <c r="L8" s="9" t="s">
+        <v>162</v>
+      </c>
+      <c r="M8" s="8">
         <v>0</v>
       </c>
-      <c r="N8" s="5">
-        <v>0.66</v>
-      </c>
-      <c r="O8" s="5">
-        <v>0.66</v>
-      </c>
-      <c r="P8" s="5">
-        <v>0.11</v>
-      </c>
-      <c r="Q8" s="5">
-        <v>6.2</v>
-      </c>
-      <c r="R8" s="5">
+      <c r="N8" s="9" t="s">
+        <v>93</v>
+      </c>
+      <c r="O8" s="9" t="s">
+        <v>93</v>
+      </c>
+      <c r="P8" s="9" t="s">
+        <v>110</v>
+      </c>
+      <c r="Q8" s="9" t="s">
+        <v>109</v>
+      </c>
+      <c r="R8" s="9">
         <v>0.32</v>
       </c>
-      <c r="S8" s="5">
-        <v>1.1000000000000001</v>
-      </c>
-      <c r="T8" s="5">
-        <v>820</v>
-      </c>
-      <c r="U8" s="5">
-        <v>1.4</v>
-      </c>
-      <c r="V8" s="5">
-        <v>2.1</v>
-      </c>
-      <c r="W8" s="5">
-        <v>9.1999999999999993</v>
+      <c r="S8" s="9" t="s">
+        <v>107</v>
+      </c>
+      <c r="T8" s="9" t="s">
+        <v>106</v>
+      </c>
+      <c r="U8" s="9" t="s">
+        <v>105</v>
+      </c>
+      <c r="V8" s="9" t="s">
+        <v>104</v>
+      </c>
+      <c r="W8" s="9" t="s">
+        <v>103</v>
       </c>
     </row>
     <row r="9" spans="1:23" ht="61.3" x14ac:dyDescent="0.4">
@@ -1861,68 +2378,68 @@
       <c r="B9" s="5" t="s">
         <v>32</v>
       </c>
-      <c r="C9" s="9" t="s">
+      <c r="C9" s="6" t="s">
         <v>30</v>
       </c>
       <c r="D9" s="5">
         <v>1600</v>
       </c>
-      <c r="E9" s="8">
-        <v>6.9999999999999994E-5</v>
-      </c>
-      <c r="F9" s="13">
-        <v>10</v>
-      </c>
-      <c r="G9" s="5">
-        <v>0.48</v>
-      </c>
-      <c r="H9" s="5">
-        <v>180</v>
-      </c>
-      <c r="I9" s="10">
-        <v>7</v>
-      </c>
-      <c r="J9" s="5">
-        <v>0.4</v>
-      </c>
-      <c r="K9" s="5">
-        <v>1400</v>
-      </c>
-      <c r="L9" s="8">
-        <v>680000000000</v>
-      </c>
-      <c r="M9" s="4">
+      <c r="E9" s="9" t="s">
+        <v>154</v>
+      </c>
+      <c r="F9" s="9" t="s">
+        <v>41</v>
+      </c>
+      <c r="G9" s="9" t="s">
+        <v>48</v>
+      </c>
+      <c r="H9" s="9" t="s">
+        <v>74</v>
+      </c>
+      <c r="I9" s="9" t="s">
+        <v>75</v>
+      </c>
+      <c r="J9" s="9" t="s">
+        <v>51</v>
+      </c>
+      <c r="K9" s="9" t="s">
+        <v>91</v>
+      </c>
+      <c r="L9" s="9" t="s">
+        <v>166</v>
+      </c>
+      <c r="M9" s="8">
         <v>0</v>
       </c>
-      <c r="N9" s="5">
-        <v>0.63</v>
-      </c>
-      <c r="O9" s="5">
-        <v>0.63</v>
-      </c>
-      <c r="P9" s="5">
-        <v>0.09</v>
-      </c>
-      <c r="Q9" s="5">
-        <v>5.8</v>
-      </c>
-      <c r="R9" s="5">
-        <v>0.28000000000000003</v>
-      </c>
-      <c r="S9" s="5">
-        <v>0.9</v>
-      </c>
-      <c r="T9" s="5">
-        <v>780</v>
-      </c>
-      <c r="U9" s="5">
-        <v>1.2</v>
-      </c>
-      <c r="V9" s="5">
-        <v>1.9</v>
-      </c>
-      <c r="W9" s="5">
-        <v>8.8000000000000007</v>
+      <c r="N9" s="9" t="s">
+        <v>96</v>
+      </c>
+      <c r="O9" s="9" t="s">
+        <v>96</v>
+      </c>
+      <c r="P9" s="9" t="s">
+        <v>111</v>
+      </c>
+      <c r="Q9" s="9" t="s">
+        <v>137</v>
+      </c>
+      <c r="R9" s="9" t="s">
+        <v>138</v>
+      </c>
+      <c r="S9" s="9" t="s">
+        <v>139</v>
+      </c>
+      <c r="T9" s="9" t="s">
+        <v>140</v>
+      </c>
+      <c r="U9" s="9" t="s">
+        <v>128</v>
+      </c>
+      <c r="V9" s="9" t="s">
+        <v>141</v>
+      </c>
+      <c r="W9" s="9" t="s">
+        <v>142</v>
       </c>
     </row>
     <row r="10" spans="1:23" ht="136.75" x14ac:dyDescent="0.4">
@@ -1932,68 +2449,68 @@
       <c r="B10" s="5" t="s">
         <v>33</v>
       </c>
-      <c r="C10" s="9" t="s">
+      <c r="C10" s="6" t="s">
         <v>30</v>
       </c>
       <c r="D10" s="5">
         <v>1900</v>
       </c>
-      <c r="E10" s="8">
-        <v>5.5000000000000002E-5</v>
-      </c>
-      <c r="F10" s="13">
-        <v>14</v>
-      </c>
-      <c r="G10" s="5">
-        <v>0.44</v>
-      </c>
-      <c r="H10" s="5">
-        <v>220</v>
-      </c>
-      <c r="I10" s="10">
-        <v>15</v>
-      </c>
-      <c r="J10" s="5">
-        <v>0.65</v>
-      </c>
-      <c r="K10" s="5">
-        <v>1200</v>
-      </c>
-      <c r="L10" s="8">
-        <v>780000000000</v>
-      </c>
-      <c r="M10" s="4">
+      <c r="E10" s="9" t="s">
+        <v>155</v>
+      </c>
+      <c r="F10" s="9" t="s">
+        <v>58</v>
+      </c>
+      <c r="G10" s="9" t="s">
+        <v>65</v>
+      </c>
+      <c r="H10" s="9" t="s">
+        <v>76</v>
+      </c>
+      <c r="I10" s="9" t="s">
+        <v>77</v>
+      </c>
+      <c r="J10" s="9" t="s">
+        <v>52</v>
+      </c>
+      <c r="K10" s="9" t="s">
+        <v>89</v>
+      </c>
+      <c r="L10" s="9" t="s">
+        <v>167</v>
+      </c>
+      <c r="M10" s="8">
         <v>0</v>
       </c>
-      <c r="N10" s="5">
-        <v>0.67</v>
-      </c>
-      <c r="O10" s="5">
-        <v>0.67</v>
-      </c>
-      <c r="P10" s="5">
-        <v>0.12</v>
-      </c>
-      <c r="Q10" s="5">
-        <v>6.5</v>
-      </c>
-      <c r="R10" s="5">
-        <v>0.35</v>
-      </c>
-      <c r="S10" s="5">
-        <v>1.2</v>
-      </c>
-      <c r="T10" s="5">
+      <c r="N10" s="9" t="s">
+        <v>94</v>
+      </c>
+      <c r="O10" s="9" t="s">
+        <v>94</v>
+      </c>
+      <c r="P10" s="9" t="s">
+        <v>122</v>
+      </c>
+      <c r="Q10" s="9" t="s">
+        <v>125</v>
+      </c>
+      <c r="R10" s="9" t="s">
+        <v>126</v>
+      </c>
+      <c r="S10" s="9" t="s">
+        <v>128</v>
+      </c>
+      <c r="T10" s="9">
         <v>850</v>
       </c>
-      <c r="U10" s="5">
-        <v>1.5</v>
-      </c>
-      <c r="V10" s="5">
-        <v>2.2000000000000002</v>
-      </c>
-      <c r="W10" s="5">
-        <v>9.5</v>
+      <c r="U10" s="9" t="s">
+        <v>130</v>
+      </c>
+      <c r="V10" s="9" t="s">
+        <v>131</v>
+      </c>
+      <c r="W10" s="9" t="s">
+        <v>133</v>
       </c>
     </row>
     <row r="11" spans="1:23" ht="92.15" x14ac:dyDescent="0.4">
@@ -2003,68 +2520,68 @@
       <c r="B11" s="5" t="s">
         <v>34</v>
       </c>
-      <c r="C11" s="9" t="s">
+      <c r="C11" s="6" t="s">
         <v>30</v>
       </c>
       <c r="D11" s="5">
         <v>1650</v>
       </c>
-      <c r="E11" s="8">
-        <v>6.2000000000000003E-5</v>
-      </c>
-      <c r="F11" s="13">
-        <v>11</v>
-      </c>
-      <c r="G11" s="5">
-        <v>0.47</v>
-      </c>
-      <c r="H11" s="5">
-        <v>250</v>
-      </c>
-      <c r="I11" s="10">
-        <v>9</v>
-      </c>
-      <c r="J11" s="5">
-        <v>0.55000000000000004</v>
-      </c>
-      <c r="K11" s="5">
-        <v>1320</v>
-      </c>
-      <c r="L11" s="8">
-        <v>700000000000</v>
-      </c>
-      <c r="M11" s="4">
+      <c r="E11" s="9" t="s">
+        <v>150</v>
+      </c>
+      <c r="F11" s="9" t="s">
+        <v>42</v>
+      </c>
+      <c r="G11" s="9" t="s">
+        <v>64</v>
+      </c>
+      <c r="H11" s="9" t="s">
+        <v>67</v>
+      </c>
+      <c r="I11" s="9" t="s">
+        <v>78</v>
+      </c>
+      <c r="J11" s="9" t="s">
+        <v>53</v>
+      </c>
+      <c r="K11" s="9" t="s">
+        <v>88</v>
+      </c>
+      <c r="L11" s="9" t="s">
+        <v>168</v>
+      </c>
+      <c r="M11" s="8">
         <v>0</v>
       </c>
-      <c r="N11" s="5">
-        <v>0.64</v>
-      </c>
-      <c r="O11" s="5">
-        <v>0.64</v>
-      </c>
-      <c r="P11" s="5">
-        <v>0.1</v>
-      </c>
-      <c r="Q11" s="5">
-        <v>6</v>
-      </c>
-      <c r="R11" s="5">
-        <v>0.3</v>
-      </c>
-      <c r="S11" s="5">
-        <v>1</v>
-      </c>
-      <c r="T11" s="5">
-        <v>800</v>
-      </c>
-      <c r="U11" s="5">
-        <v>1.3</v>
-      </c>
-      <c r="V11" s="5">
-        <v>2</v>
-      </c>
-      <c r="W11" s="5">
-        <v>9</v>
+      <c r="N11" s="9" t="s">
+        <v>97</v>
+      </c>
+      <c r="O11" s="9" t="s">
+        <v>97</v>
+      </c>
+      <c r="P11" s="9" t="s">
+        <v>121</v>
+      </c>
+      <c r="Q11" s="9" t="s">
+        <v>124</v>
+      </c>
+      <c r="R11" s="9" t="s">
+        <v>120</v>
+      </c>
+      <c r="S11" s="9" t="s">
+        <v>119</v>
+      </c>
+      <c r="T11" s="9" t="s">
+        <v>118</v>
+      </c>
+      <c r="U11" s="9" t="s">
+        <v>117</v>
+      </c>
+      <c r="V11" s="9" t="s">
+        <v>115</v>
+      </c>
+      <c r="W11" s="9" t="s">
+        <v>78</v>
       </c>
     </row>
     <row r="12" spans="1:23" ht="92.15" x14ac:dyDescent="0.4">
@@ -2074,68 +2591,68 @@
       <c r="B12" s="5" t="s">
         <v>35</v>
       </c>
-      <c r="C12" s="9" t="s">
+      <c r="C12" s="6" t="s">
         <v>30</v>
       </c>
       <c r="D12" s="5">
         <v>1880</v>
       </c>
-      <c r="E12" s="8">
-        <v>5.5999999999999999E-5</v>
-      </c>
-      <c r="F12" s="13">
-        <v>13.5</v>
-      </c>
-      <c r="G12" s="5">
-        <v>0.45</v>
-      </c>
-      <c r="H12" s="5">
-        <v>230</v>
-      </c>
-      <c r="I12" s="10">
-        <v>13</v>
-      </c>
-      <c r="J12" s="5">
-        <v>0.62</v>
-      </c>
-      <c r="K12" s="5">
-        <v>1230</v>
-      </c>
-      <c r="L12" s="8">
-        <v>760000000000</v>
-      </c>
-      <c r="M12" s="4">
+      <c r="E12" s="9" t="s">
+        <v>156</v>
+      </c>
+      <c r="F12" s="9" t="s">
+        <v>59</v>
+      </c>
+      <c r="G12" s="9" t="s">
+        <v>47</v>
+      </c>
+      <c r="H12" s="9" t="s">
+        <v>79</v>
+      </c>
+      <c r="I12" s="9" t="s">
+        <v>57</v>
+      </c>
+      <c r="J12" s="9" t="s">
+        <v>54</v>
+      </c>
+      <c r="K12" s="9" t="s">
+        <v>87</v>
+      </c>
+      <c r="L12" s="9" t="s">
+        <v>169</v>
+      </c>
+      <c r="M12" s="8">
         <v>0</v>
       </c>
-      <c r="N12" s="5">
-        <v>0.66</v>
-      </c>
-      <c r="O12" s="5">
-        <v>0.66</v>
-      </c>
-      <c r="P12" s="5">
-        <v>0.11</v>
-      </c>
-      <c r="Q12" s="5">
-        <v>6.3</v>
-      </c>
-      <c r="R12" s="5">
-        <v>0.33</v>
-      </c>
-      <c r="S12" s="5">
-        <v>1.1000000000000001</v>
-      </c>
-      <c r="T12" s="5">
-        <v>830</v>
-      </c>
-      <c r="U12" s="5">
-        <v>1.4</v>
-      </c>
-      <c r="V12" s="5">
-        <v>2.1</v>
-      </c>
-      <c r="W12" s="5">
-        <v>9.3000000000000007</v>
+      <c r="N12" s="9" t="s">
+        <v>93</v>
+      </c>
+      <c r="O12" s="9" t="s">
+        <v>93</v>
+      </c>
+      <c r="P12" s="9" t="s">
+        <v>110</v>
+      </c>
+      <c r="Q12" s="9" t="s">
+        <v>123</v>
+      </c>
+      <c r="R12" s="9" t="s">
+        <v>127</v>
+      </c>
+      <c r="S12" s="9" t="s">
+        <v>107</v>
+      </c>
+      <c r="T12" s="9" t="s">
+        <v>129</v>
+      </c>
+      <c r="U12" s="9" t="s">
+        <v>105</v>
+      </c>
+      <c r="V12" s="9" t="s">
+        <v>104</v>
+      </c>
+      <c r="W12" s="9" t="s">
+        <v>132</v>
       </c>
     </row>
     <row r="13" spans="1:23" ht="76.3" x14ac:dyDescent="0.4">
@@ -2145,68 +2662,68 @@
       <c r="B13" s="5" t="s">
         <v>36</v>
       </c>
-      <c r="C13" s="9" t="s">
+      <c r="C13" s="6" t="s">
         <v>30</v>
       </c>
       <c r="D13" s="5">
         <v>1800</v>
       </c>
-      <c r="E13" s="8">
-        <v>5.8999999999999998E-5</v>
-      </c>
-      <c r="F13" s="13">
-        <v>12.5</v>
-      </c>
-      <c r="G13" s="5">
-        <v>0.46</v>
-      </c>
-      <c r="H13" s="5">
-        <v>270</v>
-      </c>
-      <c r="I13" s="10">
-        <v>11</v>
-      </c>
-      <c r="J13" s="5">
-        <v>0.57999999999999996</v>
-      </c>
-      <c r="K13" s="5">
-        <v>1280</v>
-      </c>
-      <c r="L13" s="8">
-        <v>730000000000</v>
-      </c>
-      <c r="M13" s="4">
+      <c r="E13" s="9" t="s">
+        <v>160</v>
+      </c>
+      <c r="F13" s="9" t="s">
+        <v>60</v>
+      </c>
+      <c r="G13" s="9" t="s">
+        <v>63</v>
+      </c>
+      <c r="H13" s="9" t="s">
+        <v>71</v>
+      </c>
+      <c r="I13" s="9" t="s">
+        <v>42</v>
+      </c>
+      <c r="J13" s="9" t="s">
+        <v>55</v>
+      </c>
+      <c r="K13" s="9" t="s">
+        <v>82</v>
+      </c>
+      <c r="L13" s="9" t="s">
+        <v>163</v>
+      </c>
+      <c r="M13" s="8">
         <v>0</v>
       </c>
-      <c r="N13" s="5">
-        <v>0.65</v>
-      </c>
-      <c r="O13" s="5">
-        <v>0.65</v>
-      </c>
-      <c r="P13" s="5">
+      <c r="N13" s="9" t="s">
+        <v>52</v>
+      </c>
+      <c r="O13" s="9" t="s">
+        <v>52</v>
+      </c>
+      <c r="P13" s="9">
         <v>0.1</v>
       </c>
-      <c r="Q13" s="5">
-        <v>6.1</v>
-      </c>
-      <c r="R13" s="5">
-        <v>0.31</v>
-      </c>
-      <c r="S13" s="5">
+      <c r="Q13" s="9" t="s">
+        <v>98</v>
+      </c>
+      <c r="R13" s="9" t="s">
+        <v>99</v>
+      </c>
+      <c r="S13" s="9">
         <v>1</v>
       </c>
-      <c r="T13" s="5">
+      <c r="T13" s="9">
         <v>810</v>
       </c>
-      <c r="U13" s="5">
-        <v>1.35</v>
-      </c>
-      <c r="V13" s="5">
-        <v>2.0499999999999998</v>
-      </c>
-      <c r="W13" s="5">
-        <v>9.1</v>
+      <c r="U13" s="9" t="s">
+        <v>100</v>
+      </c>
+      <c r="V13" s="9" t="s">
+        <v>101</v>
+      </c>
+      <c r="W13" s="9" t="s">
+        <v>102</v>
       </c>
     </row>
     <row r="14" spans="1:23" ht="139.30000000000001" x14ac:dyDescent="0.4">
@@ -2216,68 +2733,68 @@
       <c r="B14" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="C14" s="9" t="s">
+      <c r="C14" s="6" t="s">
         <v>30</v>
       </c>
       <c r="D14" s="5">
         <v>1780</v>
       </c>
-      <c r="E14" s="8">
-        <v>5.7000000000000003E-5</v>
-      </c>
-      <c r="F14" s="13">
-        <v>13.2</v>
-      </c>
-      <c r="G14" s="5">
-        <v>0.45</v>
-      </c>
-      <c r="H14" s="5">
-        <v>240</v>
-      </c>
-      <c r="I14" s="10">
-        <v>12</v>
-      </c>
-      <c r="J14" s="5">
-        <v>0.6</v>
-      </c>
-      <c r="K14" s="5">
-        <v>1260</v>
-      </c>
-      <c r="L14" s="8">
-        <v>740000000000</v>
-      </c>
-      <c r="M14" s="4">
+      <c r="E14" s="9" t="s">
+        <v>159</v>
+      </c>
+      <c r="F14" s="9" t="s">
+        <v>61</v>
+      </c>
+      <c r="G14" s="9" t="s">
+        <v>47</v>
+      </c>
+      <c r="H14" s="9" t="s">
+        <v>69</v>
+      </c>
+      <c r="I14" s="9" t="s">
+        <v>45</v>
+      </c>
+      <c r="J14" s="9" t="s">
+        <v>50</v>
+      </c>
+      <c r="K14" s="9" t="s">
+        <v>86</v>
+      </c>
+      <c r="L14" s="9" t="s">
+        <v>161</v>
+      </c>
+      <c r="M14" s="8">
         <v>0</v>
       </c>
-      <c r="N14" s="5">
-        <v>0.65</v>
-      </c>
-      <c r="O14" s="5">
-        <v>0.65</v>
-      </c>
-      <c r="P14" s="5">
-        <v>0.11</v>
-      </c>
-      <c r="Q14" s="5">
-        <v>6.2</v>
-      </c>
-      <c r="R14" s="5">
-        <v>0.32</v>
-      </c>
-      <c r="S14" s="5">
-        <v>1.1000000000000001</v>
-      </c>
-      <c r="T14" s="5">
-        <v>820</v>
-      </c>
-      <c r="U14" s="5">
-        <v>1.4</v>
-      </c>
-      <c r="V14" s="5">
-        <v>2.1</v>
-      </c>
-      <c r="W14" s="5">
-        <v>9.1999999999999993</v>
+      <c r="N14" s="9" t="s">
+        <v>52</v>
+      </c>
+      <c r="O14" s="9" t="s">
+        <v>52</v>
+      </c>
+      <c r="P14" s="9" t="s">
+        <v>110</v>
+      </c>
+      <c r="Q14" s="9" t="s">
+        <v>109</v>
+      </c>
+      <c r="R14" s="9" t="s">
+        <v>108</v>
+      </c>
+      <c r="S14" s="9" t="s">
+        <v>107</v>
+      </c>
+      <c r="T14" s="9" t="s">
+        <v>106</v>
+      </c>
+      <c r="U14" s="9" t="s">
+        <v>105</v>
+      </c>
+      <c r="V14" s="9" t="s">
+        <v>104</v>
+      </c>
+      <c r="W14" s="9" t="s">
+        <v>103</v>
       </c>
     </row>
     <row r="15" spans="1:23" ht="122.15" x14ac:dyDescent="0.4">
@@ -2287,68 +2804,68 @@
       <c r="B15" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="C15" s="9" t="s">
+      <c r="C15" s="6" t="s">
         <v>30</v>
       </c>
       <c r="D15" s="5">
         <v>1680</v>
       </c>
-      <c r="E15" s="8">
-        <v>6.4999999999999994E-5</v>
-      </c>
-      <c r="F15" s="13">
-        <v>10.5</v>
-      </c>
-      <c r="G15" s="5">
-        <v>0.47</v>
-      </c>
-      <c r="H15" s="5">
-        <v>200</v>
-      </c>
-      <c r="I15" s="10">
-        <v>8</v>
-      </c>
-      <c r="J15" s="5">
-        <v>0.45</v>
-      </c>
-      <c r="K15" s="5">
-        <v>1450</v>
-      </c>
-      <c r="L15" s="8">
-        <v>690000000000</v>
-      </c>
-      <c r="M15" s="4">
+      <c r="E15" s="9" t="s">
+        <v>158</v>
+      </c>
+      <c r="F15" s="9" t="s">
+        <v>44</v>
+      </c>
+      <c r="G15" s="9" t="s">
+        <v>64</v>
+      </c>
+      <c r="H15" s="9" t="s">
+        <v>80</v>
+      </c>
+      <c r="I15" s="9" t="s">
+        <v>70</v>
+      </c>
+      <c r="J15" s="9" t="s">
+        <v>47</v>
+      </c>
+      <c r="K15" s="9" t="s">
+        <v>85</v>
+      </c>
+      <c r="L15" s="9" t="s">
+        <v>165</v>
+      </c>
+      <c r="M15" s="8">
         <v>0</v>
       </c>
-      <c r="N15" s="5">
-        <v>0.64</v>
-      </c>
-      <c r="O15" s="5">
-        <v>0.64</v>
-      </c>
-      <c r="P15" s="5">
-        <v>0.09</v>
-      </c>
-      <c r="Q15" s="5">
+      <c r="N15" s="9" t="s">
+        <v>97</v>
+      </c>
+      <c r="O15" s="9" t="s">
+        <v>97</v>
+      </c>
+      <c r="P15" s="9" t="s">
+        <v>111</v>
+      </c>
+      <c r="Q15" s="9">
         <v>5.9</v>
       </c>
-      <c r="R15" s="5">
-        <v>0.28999999999999998</v>
-      </c>
-      <c r="S15" s="5">
-        <v>0.95</v>
-      </c>
-      <c r="T15" s="5">
+      <c r="R15" s="9" t="s">
+        <v>112</v>
+      </c>
+      <c r="S15" s="9" t="s">
+        <v>113</v>
+      </c>
+      <c r="T15" s="9">
         <v>790</v>
       </c>
-      <c r="U15" s="5">
-        <v>1.25</v>
-      </c>
-      <c r="V15" s="5">
-        <v>2</v>
-      </c>
-      <c r="W15" s="5">
-        <v>8.9</v>
+      <c r="U15" s="9" t="s">
+        <v>114</v>
+      </c>
+      <c r="V15" s="9" t="s">
+        <v>115</v>
+      </c>
+      <c r="W15" s="9" t="s">
+        <v>116</v>
       </c>
     </row>
     <row r="16" spans="1:23" ht="124.75" x14ac:dyDescent="0.4">
@@ -2358,68 +2875,68 @@
       <c r="B16" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="C16" s="9" t="s">
+      <c r="C16" s="6" t="s">
         <v>30</v>
       </c>
       <c r="D16" s="5">
         <v>1720</v>
       </c>
-      <c r="E16" s="8">
-        <v>6.0999999999999999E-5</v>
-      </c>
-      <c r="F16" s="13">
-        <v>11.5</v>
-      </c>
-      <c r="G16" s="5">
-        <v>0.46</v>
-      </c>
-      <c r="H16" s="5">
-        <v>260</v>
-      </c>
-      <c r="I16" s="10">
-        <v>10</v>
-      </c>
-      <c r="J16" s="5">
-        <v>0.53</v>
-      </c>
-      <c r="K16" s="5">
-        <v>1330</v>
-      </c>
-      <c r="L16" s="8">
-        <v>710000000000</v>
-      </c>
-      <c r="M16" s="4">
+      <c r="E16" s="9" t="s">
+        <v>157</v>
+      </c>
+      <c r="F16" s="9" t="s">
+        <v>43</v>
+      </c>
+      <c r="G16" s="9" t="s">
+        <v>63</v>
+      </c>
+      <c r="H16" s="9" t="s">
+        <v>68</v>
+      </c>
+      <c r="I16" s="9" t="s">
+        <v>41</v>
+      </c>
+      <c r="J16" s="9" t="s">
+        <v>56</v>
+      </c>
+      <c r="K16" s="9" t="s">
+        <v>84</v>
+      </c>
+      <c r="L16" s="9" t="s">
+        <v>164</v>
+      </c>
+      <c r="M16" s="8">
         <v>0</v>
       </c>
-      <c r="N16" s="5">
-        <v>0.65</v>
-      </c>
-      <c r="O16" s="5">
-        <v>0.65</v>
-      </c>
-      <c r="P16" s="5">
-        <v>0.1</v>
-      </c>
-      <c r="Q16" s="5">
+      <c r="N16" s="9" t="s">
+        <v>52</v>
+      </c>
+      <c r="O16" s="9" t="s">
+        <v>52</v>
+      </c>
+      <c r="P16" s="9" t="s">
+        <v>121</v>
+      </c>
+      <c r="Q16" s="9">
         <v>6</v>
       </c>
-      <c r="R16" s="5">
-        <v>0.3</v>
-      </c>
-      <c r="S16" s="5">
-        <v>1</v>
-      </c>
-      <c r="T16" s="5">
-        <v>800</v>
-      </c>
-      <c r="U16" s="5">
-        <v>1.3</v>
-      </c>
-      <c r="V16" s="5">
-        <v>2</v>
-      </c>
-      <c r="W16" s="5">
-        <v>9</v>
+      <c r="R16" s="9" t="s">
+        <v>120</v>
+      </c>
+      <c r="S16" s="9" t="s">
+        <v>119</v>
+      </c>
+      <c r="T16" s="9" t="s">
+        <v>118</v>
+      </c>
+      <c r="U16" s="9" t="s">
+        <v>117</v>
+      </c>
+      <c r="V16" s="9" t="s">
+        <v>115</v>
+      </c>
+      <c r="W16" s="9" t="s">
+        <v>78</v>
       </c>
     </row>
   </sheetData>

--- a/mainWidget/mainWidget/src/database/推进剂材料.xlsx
+++ b/mainWidget/mainWidget/src/database/推进剂材料.xlsx
@@ -1,26 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29127"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="5" lowestEdited="4" rupBuild="9303"/>
   <workbookPr defaultThemeVersion="124226"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\VSProject\git\GFApp\mainWidget\mainWidget\src\database\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8DCEC8BF-5585-49CA-A13A-13B3593F4631}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-103" yWindow="-103" windowWidth="22149" windowHeight="13320" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-103" yWindow="-103" windowWidth="22149" windowHeight="13320"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="145621"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="307" uniqueCount="171">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="307" uniqueCount="177">
   <si>
     <r>
       <rPr>
@@ -807,6 +801,550 @@
     </r>
   </si>
   <si>
+    <t>10</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>11</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>12</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0.5</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0.45</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0.48</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0.42</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0.6</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0.4</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0.65</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0.55</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0.62</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0.58</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0.53</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>13</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0.495</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0.46</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0.47</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0.44</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>70</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>250</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>260</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>240</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>8</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>270</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>300</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>280</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>180</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>7</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>220</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>15</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>9</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>230</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>200</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1256.1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1280</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1300</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1330</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1450</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1260</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1230</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1320</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1200</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1250</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1400</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0.667</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0.66</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0.67</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0.68</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0.63</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0.64</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>6.1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0.31</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1.35</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2.05</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>9.1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>9.2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2.1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1.4</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>820</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1.1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0.32</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>6.2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0.11</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0.09</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0.29</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0.95</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1.25</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>8.9</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1.3</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>800</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0.3</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0.1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0.12</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>6.3</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>6</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>6.5</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0.35</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0.33</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1.2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>830</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1.5</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2.2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>9.3</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>9.5</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0.111</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0.333</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0.34</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>5.8</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0.28</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0.9</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>780</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1.9</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>8.8</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2.3</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>9.6</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1.8</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1.6</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>790</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>6.8</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0.000063</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0.000062</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0.00006</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0.000064</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0.000058</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0.00007</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0.000055</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0.000056</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0.000061</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0.000065</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0.000057</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0.000059</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>740000000000</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>750000000000</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>730000000000</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>710000000000</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>690000000000</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>680000000000</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>780000000000</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>700000000000</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>760000000000</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>720000000000</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>10000000</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>11000000</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>11500000</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>10500000</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>12000000</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>13000000</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>14000000</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>13500000</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>12500000</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>13200000</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>10500000</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>11500000</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
     <r>
       <rPr>
         <b/>
@@ -826,535 +1364,15 @@
         <rFont val="Times New Roman"/>
         <family val="1"/>
       </rPr>
-      <t>[GPa]</t>
+      <t>[MPa]</t>
     </r>
     <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>10</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>11</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>11.5</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>10.5</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>12</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>0.5</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>0.45</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>0.48</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>0.42</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>0.6</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>0.4</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>0.65</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>0.55</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>0.62</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>0.58</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>0.53</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>13</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>14</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>13.5</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>12.5</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>13.2</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>0.495</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>0.46</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>0.47</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>0.44</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>70</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>250</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>260</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>240</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>8</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>270</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>300</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>280</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>180</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>7</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>220</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>15</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>9</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>230</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>200</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>1256.1</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>1280</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>1300</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>1330</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>1450</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>1260</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>1230</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>1320</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>1200</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>1250</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>1400</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>0.667</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>0.66</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>0.67</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>0.68</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>0.63</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>0.64</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>6.1</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>0.31</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>1.35</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>2.05</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>9.1</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>9.2</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>2.1</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>1.4</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>820</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>1.1</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>0.32</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>6.2</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>0.11</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>0.09</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>0.29</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>0.95</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>1.25</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>2</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>8.9</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>1.3</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>800</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>1</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>0.3</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>0.1</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>0.12</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>6.3</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>6</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>6.5</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>0.35</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>0.33</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>1.2</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>830</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>1.5</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>2.2</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>9.3</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>9.5</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>0.111</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>0.333</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>0.34</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>5.8</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>0.28</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>0.9</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>780</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>1.9</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>8.8</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>2.3</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>9.6</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>1.8</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>1.6</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>790</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>6.8</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>0.000063</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>0.000062</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>0.00006</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>0.000064</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>0.000058</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>0.00007</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>0.000055</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>0.000056</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>0.000061</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>0.000065</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>0.000057</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>0.000059</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>740000000000</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>750000000000</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>730000000000</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>710000000000</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>690000000000</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>680000000000</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>780000000000</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>700000000000</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>760000000000</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>720000000000</t>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <numFmts count="1">
     <numFmt numFmtId="176" formatCode="0;[Red]0"/>
   </numFmts>
@@ -1508,9 +1526,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 主题​​">
   <a:themeElements>
-    <a:clrScheme name="Office 2007 - 2010">
+    <a:clrScheme name="Office">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -1548,7 +1566,7 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office 2007 - 2010">
+    <a:fontScheme name="Office">
       <a:majorFont>
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
@@ -1620,7 +1638,7 @@
         <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office 2007 - 2010">
+    <a:fmtScheme name="Office">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -1793,7 +1811,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:W16"/>
   <sheetFormatPr defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
   <cols>
@@ -1820,7 +1838,7 @@
         <v>4</v>
       </c>
       <c r="F1" s="7" t="s">
-        <v>40</v>
+        <v>176</v>
       </c>
       <c r="G1" s="1" t="s">
         <v>5</v>
@@ -1888,61 +1906,61 @@
         <v>1750</v>
       </c>
       <c r="E2" s="8" t="s">
-        <v>149</v>
+        <v>142</v>
       </c>
       <c r="F2" s="8" t="s">
-        <v>41</v>
+        <v>164</v>
       </c>
       <c r="G2" s="8" t="s">
-        <v>62</v>
+        <v>55</v>
       </c>
       <c r="H2" s="8" t="s">
-        <v>66</v>
+        <v>59</v>
       </c>
       <c r="I2" s="8" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="J2" s="8" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="K2" s="8" t="s">
-        <v>81</v>
+        <v>74</v>
       </c>
       <c r="L2" s="8" t="s">
-        <v>161</v>
+        <v>154</v>
       </c>
       <c r="M2" s="8">
         <v>0</v>
       </c>
       <c r="N2" s="8" t="s">
-        <v>92</v>
+        <v>85</v>
       </c>
       <c r="O2" s="8" t="s">
-        <v>92</v>
+        <v>85</v>
       </c>
       <c r="P2" s="8" t="s">
-        <v>134</v>
+        <v>127</v>
       </c>
       <c r="Q2" s="8" t="s">
-        <v>75</v>
+        <v>68</v>
       </c>
       <c r="R2" s="8" t="s">
-        <v>135</v>
+        <v>128</v>
       </c>
       <c r="S2" s="8" t="s">
-        <v>119</v>
+        <v>112</v>
       </c>
       <c r="T2" s="8" t="s">
-        <v>118</v>
+        <v>111</v>
       </c>
       <c r="U2" s="8" t="s">
-        <v>130</v>
+        <v>123</v>
       </c>
       <c r="V2" s="8" t="s">
-        <v>115</v>
+        <v>108</v>
       </c>
       <c r="W2" s="8" t="s">
-        <v>144</v>
+        <v>137</v>
       </c>
     </row>
     <row r="3" spans="1:23" ht="30" x14ac:dyDescent="0.4">
@@ -1959,61 +1977,61 @@
         <v>1700</v>
       </c>
       <c r="E3" s="9" t="s">
-        <v>150</v>
+        <v>143</v>
       </c>
       <c r="F3" s="9" t="s">
-        <v>42</v>
+        <v>165</v>
       </c>
       <c r="G3" s="9" t="s">
-        <v>63</v>
+        <v>56</v>
       </c>
       <c r="H3" s="9" t="s">
-        <v>67</v>
+        <v>60</v>
       </c>
       <c r="I3" s="9">
         <v>9</v>
       </c>
       <c r="J3" s="9" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="K3" s="9" t="s">
-        <v>82</v>
+        <v>75</v>
       </c>
       <c r="L3" s="8" t="s">
-        <v>162</v>
+        <v>155</v>
       </c>
       <c r="M3" s="9">
         <v>0</v>
       </c>
       <c r="N3" s="9" t="s">
-        <v>93</v>
+        <v>86</v>
       </c>
       <c r="O3" s="9" t="s">
-        <v>93</v>
+        <v>86</v>
       </c>
       <c r="P3" s="9" t="s">
-        <v>110</v>
+        <v>103</v>
       </c>
       <c r="Q3" s="9" t="s">
-        <v>125</v>
+        <v>118</v>
       </c>
       <c r="R3" s="9" t="s">
-        <v>136</v>
+        <v>129</v>
       </c>
       <c r="S3" s="9" t="s">
-        <v>119</v>
+        <v>112</v>
       </c>
       <c r="T3" s="9" t="s">
-        <v>118</v>
+        <v>111</v>
       </c>
       <c r="U3" s="9" t="s">
-        <v>105</v>
+        <v>98</v>
       </c>
       <c r="V3" s="9" t="s">
-        <v>141</v>
+        <v>134</v>
       </c>
       <c r="W3" s="9" t="s">
-        <v>104</v>
+        <v>97</v>
       </c>
     </row>
     <row r="4" spans="1:23" ht="30" x14ac:dyDescent="0.4">
@@ -2030,61 +2048,61 @@
         <v>1780</v>
       </c>
       <c r="E4" s="9" t="s">
-        <v>149</v>
+        <v>142</v>
       </c>
       <c r="F4" s="9" t="s">
-        <v>43</v>
+        <v>166</v>
       </c>
       <c r="G4" s="9" t="s">
-        <v>64</v>
+        <v>57</v>
       </c>
       <c r="H4" s="9" t="s">
-        <v>68</v>
+        <v>61</v>
       </c>
       <c r="I4" s="9" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="J4" s="9" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="K4" s="9" t="s">
-        <v>83</v>
+        <v>76</v>
       </c>
       <c r="L4" s="8" t="s">
-        <v>163</v>
+        <v>156</v>
       </c>
       <c r="M4" s="9">
         <v>0</v>
       </c>
       <c r="N4" s="9" t="s">
-        <v>94</v>
+        <v>87</v>
       </c>
       <c r="O4" s="9">
         <v>0.67</v>
       </c>
       <c r="P4" s="9" t="s">
-        <v>122</v>
+        <v>115</v>
       </c>
       <c r="Q4" s="9" t="s">
-        <v>148</v>
+        <v>141</v>
       </c>
       <c r="R4" s="9" t="s">
-        <v>126</v>
+        <v>119</v>
       </c>
       <c r="S4" s="9" t="s">
-        <v>107</v>
+        <v>100</v>
       </c>
       <c r="T4" s="9" t="s">
-        <v>106</v>
+        <v>99</v>
       </c>
       <c r="U4" s="9" t="s">
-        <v>130</v>
+        <v>123</v>
       </c>
       <c r="V4" s="9" t="s">
-        <v>115</v>
+        <v>108</v>
       </c>
       <c r="W4" s="9" t="s">
-        <v>131</v>
+        <v>124</v>
       </c>
     </row>
     <row r="5" spans="1:23" ht="15.45" x14ac:dyDescent="0.4">
@@ -2101,61 +2119,61 @@
         <v>1650</v>
       </c>
       <c r="E5" s="9" t="s">
-        <v>151</v>
+        <v>144</v>
       </c>
       <c r="F5" s="9" t="s">
+        <v>167</v>
+      </c>
+      <c r="G5" s="9" t="s">
         <v>44</v>
       </c>
-      <c r="G5" s="9" t="s">
-        <v>47</v>
-      </c>
       <c r="H5" s="9" t="s">
-        <v>69</v>
+        <v>62</v>
       </c>
       <c r="I5" s="9" t="s">
-        <v>70</v>
+        <v>63</v>
       </c>
       <c r="J5" s="9" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="K5" s="9" t="s">
-        <v>90</v>
+        <v>83</v>
       </c>
       <c r="L5" s="8" t="s">
-        <v>162</v>
+        <v>155</v>
       </c>
       <c r="M5" s="9">
         <v>0</v>
       </c>
       <c r="N5" s="9" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="O5" s="9" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="P5" s="9" t="s">
-        <v>121</v>
+        <v>114</v>
       </c>
       <c r="Q5" s="9" t="s">
-        <v>109</v>
+        <v>102</v>
       </c>
       <c r="R5" s="9" t="s">
+        <v>101</v>
+      </c>
+      <c r="S5" s="9" t="s">
+        <v>112</v>
+      </c>
+      <c r="T5" s="9" t="s">
+        <v>140</v>
+      </c>
+      <c r="U5" s="9" t="s">
+        <v>110</v>
+      </c>
+      <c r="V5" s="9" t="s">
+        <v>138</v>
+      </c>
+      <c r="W5" s="9" t="s">
         <v>108</v>
-      </c>
-      <c r="S5" s="9" t="s">
-        <v>119</v>
-      </c>
-      <c r="T5" s="9" t="s">
-        <v>147</v>
-      </c>
-      <c r="U5" s="9" t="s">
-        <v>117</v>
-      </c>
-      <c r="V5" s="9" t="s">
-        <v>145</v>
-      </c>
-      <c r="W5" s="9" t="s">
-        <v>115</v>
       </c>
     </row>
     <row r="6" spans="1:23" ht="30.9" x14ac:dyDescent="0.4">
@@ -2172,34 +2190,34 @@
         <v>1820</v>
       </c>
       <c r="E6" s="9" t="s">
-        <v>152</v>
+        <v>145</v>
       </c>
       <c r="F6" s="9" t="s">
+        <v>168</v>
+      </c>
+      <c r="G6" s="9" t="s">
         <v>45</v>
       </c>
-      <c r="G6" s="9" t="s">
-        <v>48</v>
-      </c>
       <c r="H6" s="9" t="s">
-        <v>71</v>
+        <v>64</v>
       </c>
       <c r="I6" s="9" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="J6" s="9" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="K6" s="9" t="s">
-        <v>88</v>
+        <v>81</v>
       </c>
       <c r="L6" s="9" t="s">
-        <v>167</v>
+        <v>160</v>
       </c>
       <c r="M6" s="9">
         <v>0</v>
       </c>
       <c r="N6" s="9" t="s">
-        <v>95</v>
+        <v>88</v>
       </c>
       <c r="O6" s="9">
         <v>0.68</v>
@@ -2220,13 +2238,13 @@
         <v>830</v>
       </c>
       <c r="U6" s="9" t="s">
-        <v>146</v>
+        <v>139</v>
       </c>
       <c r="V6" s="9" t="s">
-        <v>104</v>
+        <v>97</v>
       </c>
       <c r="W6" s="9" t="s">
-        <v>143</v>
+        <v>136</v>
       </c>
     </row>
     <row r="7" spans="1:23" ht="92.15" x14ac:dyDescent="0.4">
@@ -2243,61 +2261,61 @@
         <v>1750</v>
       </c>
       <c r="E7" s="9" t="s">
-        <v>151</v>
+        <v>144</v>
       </c>
       <c r="F7" s="9" t="s">
-        <v>45</v>
+        <v>168</v>
       </c>
       <c r="G7" s="9" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="H7" s="9" t="s">
-        <v>72</v>
+        <v>65</v>
       </c>
       <c r="I7" s="9" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="J7" s="9" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="K7" s="9" t="s">
-        <v>83</v>
+        <v>76</v>
       </c>
       <c r="L7" s="9" t="s">
-        <v>170</v>
+        <v>163</v>
       </c>
       <c r="M7" s="8">
         <v>0</v>
       </c>
       <c r="N7" s="9" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="O7" s="9" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="P7" s="9" t="s">
-        <v>121</v>
+        <v>114</v>
       </c>
       <c r="Q7" s="9" t="s">
-        <v>124</v>
+        <v>117</v>
       </c>
       <c r="R7" s="9" t="s">
-        <v>120</v>
+        <v>113</v>
       </c>
       <c r="S7" s="9" t="s">
-        <v>119</v>
+        <v>112</v>
       </c>
       <c r="T7" s="9" t="s">
-        <v>118</v>
+        <v>111</v>
       </c>
       <c r="U7" s="9" t="s">
-        <v>117</v>
+        <v>110</v>
       </c>
       <c r="V7" s="9" t="s">
-        <v>115</v>
+        <v>108</v>
       </c>
       <c r="W7" s="9" t="s">
-        <v>78</v>
+        <v>71</v>
       </c>
     </row>
     <row r="8" spans="1:23" ht="108" x14ac:dyDescent="0.4">
@@ -2314,61 +2332,61 @@
         <v>1850</v>
       </c>
       <c r="E8" s="9" t="s">
-        <v>153</v>
+        <v>146</v>
       </c>
       <c r="F8" s="9" t="s">
-        <v>57</v>
+        <v>169</v>
       </c>
       <c r="G8" s="9" t="s">
-        <v>63</v>
+        <v>56</v>
       </c>
       <c r="H8" s="9" t="s">
-        <v>73</v>
+        <v>66</v>
       </c>
       <c r="I8" s="9" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="J8" s="9" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="K8" s="9" t="s">
-        <v>90</v>
+        <v>83</v>
       </c>
       <c r="L8" s="9" t="s">
-        <v>162</v>
+        <v>155</v>
       </c>
       <c r="M8" s="8">
         <v>0</v>
       </c>
       <c r="N8" s="9" t="s">
-        <v>93</v>
+        <v>86</v>
       </c>
       <c r="O8" s="9" t="s">
-        <v>93</v>
+        <v>86</v>
       </c>
       <c r="P8" s="9" t="s">
-        <v>110</v>
+        <v>103</v>
       </c>
       <c r="Q8" s="9" t="s">
-        <v>109</v>
+        <v>102</v>
       </c>
       <c r="R8" s="9">
         <v>0.32</v>
       </c>
       <c r="S8" s="9" t="s">
-        <v>107</v>
+        <v>100</v>
       </c>
       <c r="T8" s="9" t="s">
-        <v>106</v>
+        <v>99</v>
       </c>
       <c r="U8" s="9" t="s">
-        <v>105</v>
+        <v>98</v>
       </c>
       <c r="V8" s="9" t="s">
-        <v>104</v>
+        <v>97</v>
       </c>
       <c r="W8" s="9" t="s">
-        <v>103</v>
+        <v>96</v>
       </c>
     </row>
     <row r="9" spans="1:23" ht="61.3" x14ac:dyDescent="0.4">
@@ -2385,61 +2403,61 @@
         <v>1600</v>
       </c>
       <c r="E9" s="9" t="s">
-        <v>154</v>
+        <v>147</v>
       </c>
       <c r="F9" s="9" t="s">
-        <v>41</v>
+        <v>164</v>
       </c>
       <c r="G9" s="9" t="s">
+        <v>45</v>
+      </c>
+      <c r="H9" s="9" t="s">
+        <v>67</v>
+      </c>
+      <c r="I9" s="9" t="s">
+        <v>68</v>
+      </c>
+      <c r="J9" s="9" t="s">
         <v>48</v>
       </c>
-      <c r="H9" s="9" t="s">
-        <v>74</v>
-      </c>
-      <c r="I9" s="9" t="s">
-        <v>75</v>
-      </c>
-      <c r="J9" s="9" t="s">
-        <v>51</v>
-      </c>
       <c r="K9" s="9" t="s">
-        <v>91</v>
+        <v>84</v>
       </c>
       <c r="L9" s="9" t="s">
-        <v>166</v>
+        <v>159</v>
       </c>
       <c r="M9" s="8">
         <v>0</v>
       </c>
       <c r="N9" s="9" t="s">
-        <v>96</v>
+        <v>89</v>
       </c>
       <c r="O9" s="9" t="s">
-        <v>96</v>
+        <v>89</v>
       </c>
       <c r="P9" s="9" t="s">
-        <v>111</v>
+        <v>104</v>
       </c>
       <c r="Q9" s="9" t="s">
-        <v>137</v>
+        <v>130</v>
       </c>
       <c r="R9" s="9" t="s">
-        <v>138</v>
+        <v>131</v>
       </c>
       <c r="S9" s="9" t="s">
-        <v>139</v>
+        <v>132</v>
       </c>
       <c r="T9" s="9" t="s">
-        <v>140</v>
+        <v>133</v>
       </c>
       <c r="U9" s="9" t="s">
-        <v>128</v>
+        <v>121</v>
       </c>
       <c r="V9" s="9" t="s">
-        <v>141</v>
+        <v>134</v>
       </c>
       <c r="W9" s="9" t="s">
-        <v>142</v>
+        <v>135</v>
       </c>
     </row>
     <row r="10" spans="1:23" ht="136.75" x14ac:dyDescent="0.4">
@@ -2456,61 +2474,61 @@
         <v>1900</v>
       </c>
       <c r="E10" s="9" t="s">
-        <v>155</v>
+        <v>148</v>
       </c>
       <c r="F10" s="9" t="s">
+        <v>170</v>
+      </c>
+      <c r="G10" s="9" t="s">
         <v>58</v>
       </c>
-      <c r="G10" s="9" t="s">
-        <v>65</v>
-      </c>
       <c r="H10" s="9" t="s">
-        <v>76</v>
+        <v>69</v>
       </c>
       <c r="I10" s="9" t="s">
-        <v>77</v>
+        <v>70</v>
       </c>
       <c r="J10" s="9" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="K10" s="9" t="s">
-        <v>89</v>
+        <v>82</v>
       </c>
       <c r="L10" s="9" t="s">
-        <v>167</v>
+        <v>160</v>
       </c>
       <c r="M10" s="8">
         <v>0</v>
       </c>
       <c r="N10" s="9" t="s">
-        <v>94</v>
+        <v>87</v>
       </c>
       <c r="O10" s="9" t="s">
-        <v>94</v>
+        <v>87</v>
       </c>
       <c r="P10" s="9" t="s">
-        <v>122</v>
+        <v>115</v>
       </c>
       <c r="Q10" s="9" t="s">
-        <v>125</v>
+        <v>118</v>
       </c>
       <c r="R10" s="9" t="s">
-        <v>126</v>
+        <v>119</v>
       </c>
       <c r="S10" s="9" t="s">
-        <v>128</v>
+        <v>121</v>
       </c>
       <c r="T10" s="9">
         <v>850</v>
       </c>
       <c r="U10" s="9" t="s">
-        <v>130</v>
+        <v>123</v>
       </c>
       <c r="V10" s="9" t="s">
-        <v>131</v>
+        <v>124</v>
       </c>
       <c r="W10" s="9" t="s">
-        <v>133</v>
+        <v>126</v>
       </c>
     </row>
     <row r="11" spans="1:23" ht="92.15" x14ac:dyDescent="0.4">
@@ -2527,61 +2545,61 @@
         <v>1650</v>
       </c>
       <c r="E11" s="9" t="s">
-        <v>150</v>
+        <v>143</v>
       </c>
       <c r="F11" s="9" t="s">
-        <v>42</v>
+        <v>165</v>
       </c>
       <c r="G11" s="9" t="s">
-        <v>64</v>
+        <v>57</v>
       </c>
       <c r="H11" s="9" t="s">
-        <v>67</v>
+        <v>60</v>
       </c>
       <c r="I11" s="9" t="s">
-        <v>78</v>
+        <v>71</v>
       </c>
       <c r="J11" s="9" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="K11" s="9" t="s">
-        <v>88</v>
+        <v>81</v>
       </c>
       <c r="L11" s="9" t="s">
-        <v>168</v>
+        <v>161</v>
       </c>
       <c r="M11" s="8">
         <v>0</v>
       </c>
       <c r="N11" s="9" t="s">
-        <v>97</v>
+        <v>90</v>
       </c>
       <c r="O11" s="9" t="s">
-        <v>97</v>
+        <v>90</v>
       </c>
       <c r="P11" s="9" t="s">
-        <v>121</v>
+        <v>114</v>
       </c>
       <c r="Q11" s="9" t="s">
-        <v>124</v>
+        <v>117</v>
       </c>
       <c r="R11" s="9" t="s">
-        <v>120</v>
+        <v>113</v>
       </c>
       <c r="S11" s="9" t="s">
-        <v>119</v>
+        <v>112</v>
       </c>
       <c r="T11" s="9" t="s">
-        <v>118</v>
+        <v>111</v>
       </c>
       <c r="U11" s="9" t="s">
-        <v>117</v>
+        <v>110</v>
       </c>
       <c r="V11" s="9" t="s">
-        <v>115</v>
+        <v>108</v>
       </c>
       <c r="W11" s="9" t="s">
-        <v>78</v>
+        <v>71</v>
       </c>
     </row>
     <row r="12" spans="1:23" ht="92.15" x14ac:dyDescent="0.4">
@@ -2598,61 +2616,61 @@
         <v>1880</v>
       </c>
       <c r="E12" s="9" t="s">
-        <v>156</v>
+        <v>149</v>
       </c>
       <c r="F12" s="9" t="s">
-        <v>59</v>
+        <v>171</v>
       </c>
       <c r="G12" s="9" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="H12" s="9" t="s">
-        <v>79</v>
+        <v>72</v>
       </c>
       <c r="I12" s="9" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="J12" s="9" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="K12" s="9" t="s">
-        <v>87</v>
+        <v>80</v>
       </c>
       <c r="L12" s="9" t="s">
-        <v>169</v>
+        <v>162</v>
       </c>
       <c r="M12" s="8">
         <v>0</v>
       </c>
       <c r="N12" s="9" t="s">
-        <v>93</v>
+        <v>86</v>
       </c>
       <c r="O12" s="9" t="s">
-        <v>93</v>
+        <v>86</v>
       </c>
       <c r="P12" s="9" t="s">
-        <v>110</v>
+        <v>103</v>
       </c>
       <c r="Q12" s="9" t="s">
-        <v>123</v>
+        <v>116</v>
       </c>
       <c r="R12" s="9" t="s">
-        <v>127</v>
+        <v>120</v>
       </c>
       <c r="S12" s="9" t="s">
-        <v>107</v>
+        <v>100</v>
       </c>
       <c r="T12" s="9" t="s">
-        <v>129</v>
+        <v>122</v>
       </c>
       <c r="U12" s="9" t="s">
-        <v>105</v>
+        <v>98</v>
       </c>
       <c r="V12" s="9" t="s">
-        <v>104</v>
+        <v>97</v>
       </c>
       <c r="W12" s="9" t="s">
-        <v>132</v>
+        <v>125</v>
       </c>
     </row>
     <row r="13" spans="1:23" ht="76.3" x14ac:dyDescent="0.4">
@@ -2669,46 +2687,46 @@
         <v>1800</v>
       </c>
       <c r="E13" s="9" t="s">
-        <v>160</v>
+        <v>153</v>
       </c>
       <c r="F13" s="9" t="s">
-        <v>60</v>
+        <v>172</v>
       </c>
       <c r="G13" s="9" t="s">
-        <v>63</v>
+        <v>56</v>
       </c>
       <c r="H13" s="9" t="s">
-        <v>71</v>
+        <v>64</v>
       </c>
       <c r="I13" s="9" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="J13" s="9" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="K13" s="9" t="s">
-        <v>82</v>
+        <v>75</v>
       </c>
       <c r="L13" s="9" t="s">
-        <v>163</v>
+        <v>156</v>
       </c>
       <c r="M13" s="8">
         <v>0</v>
       </c>
       <c r="N13" s="9" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="O13" s="9" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="P13" s="9">
         <v>0.1</v>
       </c>
       <c r="Q13" s="9" t="s">
-        <v>98</v>
+        <v>91</v>
       </c>
       <c r="R13" s="9" t="s">
-        <v>99</v>
+        <v>92</v>
       </c>
       <c r="S13" s="9">
         <v>1</v>
@@ -2717,13 +2735,13 @@
         <v>810</v>
       </c>
       <c r="U13" s="9" t="s">
-        <v>100</v>
+        <v>93</v>
       </c>
       <c r="V13" s="9" t="s">
-        <v>101</v>
+        <v>94</v>
       </c>
       <c r="W13" s="9" t="s">
-        <v>102</v>
+        <v>95</v>
       </c>
     </row>
     <row r="14" spans="1:23" ht="139.30000000000001" x14ac:dyDescent="0.4">
@@ -2740,61 +2758,61 @@
         <v>1780</v>
       </c>
       <c r="E14" s="9" t="s">
-        <v>159</v>
+        <v>152</v>
       </c>
       <c r="F14" s="9" t="s">
-        <v>61</v>
+        <v>173</v>
       </c>
       <c r="G14" s="9" t="s">
+        <v>44</v>
+      </c>
+      <c r="H14" s="9" t="s">
+        <v>62</v>
+      </c>
+      <c r="I14" s="9" t="s">
+        <v>42</v>
+      </c>
+      <c r="J14" s="9" t="s">
         <v>47</v>
       </c>
-      <c r="H14" s="9" t="s">
-        <v>69</v>
-      </c>
-      <c r="I14" s="9" t="s">
-        <v>45</v>
-      </c>
-      <c r="J14" s="9" t="s">
-        <v>50</v>
-      </c>
       <c r="K14" s="9" t="s">
-        <v>86</v>
+        <v>79</v>
       </c>
       <c r="L14" s="9" t="s">
-        <v>161</v>
+        <v>154</v>
       </c>
       <c r="M14" s="8">
         <v>0</v>
       </c>
       <c r="N14" s="9" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="O14" s="9" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="P14" s="9" t="s">
-        <v>110</v>
+        <v>103</v>
       </c>
       <c r="Q14" s="9" t="s">
-        <v>109</v>
+        <v>102</v>
       </c>
       <c r="R14" s="9" t="s">
-        <v>108</v>
+        <v>101</v>
       </c>
       <c r="S14" s="9" t="s">
-        <v>107</v>
+        <v>100</v>
       </c>
       <c r="T14" s="9" t="s">
-        <v>106</v>
+        <v>99</v>
       </c>
       <c r="U14" s="9" t="s">
-        <v>105</v>
+        <v>98</v>
       </c>
       <c r="V14" s="9" t="s">
-        <v>104</v>
+        <v>97</v>
       </c>
       <c r="W14" s="9" t="s">
-        <v>103</v>
+        <v>96</v>
       </c>
     </row>
     <row r="15" spans="1:23" ht="122.15" x14ac:dyDescent="0.4">
@@ -2811,61 +2829,61 @@
         <v>1680</v>
       </c>
       <c r="E15" s="9" t="s">
+        <v>151</v>
+      </c>
+      <c r="F15" s="9" t="s">
+        <v>174</v>
+      </c>
+      <c r="G15" s="9" t="s">
+        <v>57</v>
+      </c>
+      <c r="H15" s="9" t="s">
+        <v>73</v>
+      </c>
+      <c r="I15" s="9" t="s">
+        <v>63</v>
+      </c>
+      <c r="J15" s="9" t="s">
+        <v>44</v>
+      </c>
+      <c r="K15" s="9" t="s">
+        <v>78</v>
+      </c>
+      <c r="L15" s="9" t="s">
         <v>158</v>
-      </c>
-      <c r="F15" s="9" t="s">
-        <v>44</v>
-      </c>
-      <c r="G15" s="9" t="s">
-        <v>64</v>
-      </c>
-      <c r="H15" s="9" t="s">
-        <v>80</v>
-      </c>
-      <c r="I15" s="9" t="s">
-        <v>70</v>
-      </c>
-      <c r="J15" s="9" t="s">
-        <v>47</v>
-      </c>
-      <c r="K15" s="9" t="s">
-        <v>85</v>
-      </c>
-      <c r="L15" s="9" t="s">
-        <v>165</v>
       </c>
       <c r="M15" s="8">
         <v>0</v>
       </c>
       <c r="N15" s="9" t="s">
-        <v>97</v>
+        <v>90</v>
       </c>
       <c r="O15" s="9" t="s">
-        <v>97</v>
+        <v>90</v>
       </c>
       <c r="P15" s="9" t="s">
-        <v>111</v>
+        <v>104</v>
       </c>
       <c r="Q15" s="9">
         <v>5.9</v>
       </c>
       <c r="R15" s="9" t="s">
-        <v>112</v>
+        <v>105</v>
       </c>
       <c r="S15" s="9" t="s">
-        <v>113</v>
+        <v>106</v>
       </c>
       <c r="T15" s="9">
         <v>790</v>
       </c>
       <c r="U15" s="9" t="s">
-        <v>114</v>
+        <v>107</v>
       </c>
       <c r="V15" s="9" t="s">
-        <v>115</v>
+        <v>108</v>
       </c>
       <c r="W15" s="9" t="s">
-        <v>116</v>
+        <v>109</v>
       </c>
     </row>
     <row r="16" spans="1:23" ht="124.75" x14ac:dyDescent="0.4">
@@ -2882,61 +2900,61 @@
         <v>1720</v>
       </c>
       <c r="E16" s="9" t="s">
+        <v>150</v>
+      </c>
+      <c r="F16" s="9" t="s">
+        <v>175</v>
+      </c>
+      <c r="G16" s="9" t="s">
+        <v>56</v>
+      </c>
+      <c r="H16" s="9" t="s">
+        <v>61</v>
+      </c>
+      <c r="I16" s="9" t="s">
+        <v>40</v>
+      </c>
+      <c r="J16" s="9" t="s">
+        <v>53</v>
+      </c>
+      <c r="K16" s="9" t="s">
+        <v>77</v>
+      </c>
+      <c r="L16" s="9" t="s">
         <v>157</v>
-      </c>
-      <c r="F16" s="9" t="s">
-        <v>43</v>
-      </c>
-      <c r="G16" s="9" t="s">
-        <v>63</v>
-      </c>
-      <c r="H16" s="9" t="s">
-        <v>68</v>
-      </c>
-      <c r="I16" s="9" t="s">
-        <v>41</v>
-      </c>
-      <c r="J16" s="9" t="s">
-        <v>56</v>
-      </c>
-      <c r="K16" s="9" t="s">
-        <v>84</v>
-      </c>
-      <c r="L16" s="9" t="s">
-        <v>164</v>
       </c>
       <c r="M16" s="8">
         <v>0</v>
       </c>
       <c r="N16" s="9" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="O16" s="9" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="P16" s="9" t="s">
-        <v>121</v>
+        <v>114</v>
       </c>
       <c r="Q16" s="9">
         <v>6</v>
       </c>
       <c r="R16" s="9" t="s">
-        <v>120</v>
+        <v>113</v>
       </c>
       <c r="S16" s="9" t="s">
-        <v>119</v>
+        <v>112</v>
       </c>
       <c r="T16" s="9" t="s">
-        <v>118</v>
+        <v>111</v>
       </c>
       <c r="U16" s="9" t="s">
-        <v>117</v>
+        <v>110</v>
       </c>
       <c r="V16" s="9" t="s">
-        <v>115</v>
+        <v>108</v>
       </c>
       <c r="W16" s="9" t="s">
-        <v>78</v>
+        <v>71</v>
       </c>
     </row>
   </sheetData>

--- a/mainWidget/mainWidget/src/database/推进剂材料.xlsx
+++ b/mainWidget/mainWidget/src/database/推进剂材料.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="340" uniqueCount="196">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="357" uniqueCount="200">
   <si>
     <r>
       <rPr>
@@ -1549,6 +1549,20 @@
   <si>
     <t>140</t>
     <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>感度</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>感度类型</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>撞击</t>
+  </si>
+  <si>
+    <t>摩擦</t>
   </si>
 </sst>
 </file>
@@ -1558,7 +1572,7 @@
   <numFmts count="1">
     <numFmt numFmtId="176" formatCode="0;[Red]0"/>
   </numFmts>
-  <fonts count="9" x14ac:knownFonts="1">
+  <fonts count="10" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <name val="Calibri"/>
@@ -1620,6 +1634,13 @@
       <family val="3"/>
       <charset val="134"/>
     </font>
+    <font>
+      <sz val="12"/>
+      <color rgb="FF000000"/>
+      <name val="仿宋"/>
+      <family val="3"/>
+      <charset val="134"/>
+    </font>
   </fonts>
   <fills count="3">
     <fill>
@@ -1662,7 +1683,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1698,6 +1719,10 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="49" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -2002,8 +2027,8 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:Y16"/>
-  <sheetFormatPr defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
+  <dimension ref="A1:AA16"/>
+  <sheetFormatPr defaultRowHeight="15.45" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="5" max="5" width="9.23046875" style="12"/>
     <col min="6" max="7" width="18" customWidth="1"/>
@@ -2012,9 +2037,10 @@
     <col min="11" max="11" width="22.3046875" customWidth="1"/>
     <col min="14" max="14" width="12.07421875" style="12" customWidth="1"/>
     <col min="15" max="25" width="9.23046875" style="12"/>
+    <col min="26" max="27" width="9.23046875" style="9"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:25" ht="15" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:27" ht="15" x14ac:dyDescent="0.4">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2090,8 +2116,14 @@
       <c r="Y1" s="10" t="s">
         <v>18</v>
       </c>
+      <c r="Z1" s="10" t="s">
+        <v>196</v>
+      </c>
+      <c r="AA1" s="13" t="s">
+        <v>197</v>
+      </c>
     </row>
-    <row r="2" spans="1:25" ht="15.45" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:27" ht="15.9" x14ac:dyDescent="0.4">
       <c r="A2" s="4">
         <v>1</v>
       </c>
@@ -2167,8 +2199,14 @@
       <c r="Y2" s="8" t="s">
         <v>128</v>
       </c>
+      <c r="Z2" s="9">
+        <v>1</v>
+      </c>
+      <c r="AA2" s="14" t="s">
+        <v>198</v>
+      </c>
     </row>
-    <row r="3" spans="1:25" ht="30" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:27" ht="30" x14ac:dyDescent="0.4">
       <c r="A3" s="4">
         <v>2</v>
       </c>
@@ -2244,8 +2282,14 @@
       <c r="Y3" s="9" t="s">
         <v>88</v>
       </c>
+      <c r="Z3" s="9">
+        <v>1</v>
+      </c>
+      <c r="AA3" s="14" t="s">
+        <v>199</v>
+      </c>
     </row>
-    <row r="4" spans="1:25" ht="30" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:27" ht="30" x14ac:dyDescent="0.4">
       <c r="A4" s="4">
         <v>3</v>
       </c>
@@ -2321,8 +2365,14 @@
       <c r="Y4" s="9" t="s">
         <v>115</v>
       </c>
+      <c r="Z4" s="9">
+        <v>1</v>
+      </c>
+      <c r="AA4" s="14" t="s">
+        <v>198</v>
+      </c>
     </row>
-    <row r="5" spans="1:25" ht="15.45" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:27" ht="15.9" x14ac:dyDescent="0.4">
       <c r="A5" s="4">
         <v>4</v>
       </c>
@@ -2398,8 +2448,14 @@
       <c r="Y5" s="9" t="s">
         <v>99</v>
       </c>
+      <c r="Z5" s="9">
+        <v>1</v>
+      </c>
+      <c r="AA5" s="14" t="s">
+        <v>199</v>
+      </c>
     </row>
-    <row r="6" spans="1:25" ht="30.9" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:27" ht="30.9" x14ac:dyDescent="0.4">
       <c r="A6" s="4">
         <v>5</v>
       </c>
@@ -2475,8 +2531,14 @@
       <c r="Y6" s="9" t="s">
         <v>127</v>
       </c>
+      <c r="Z6" s="9">
+        <v>1</v>
+      </c>
+      <c r="AA6" s="14" t="s">
+        <v>198</v>
+      </c>
     </row>
-    <row r="7" spans="1:25" ht="92.15" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:27" ht="92.15" x14ac:dyDescent="0.4">
       <c r="A7" s="4">
         <v>6</v>
       </c>
@@ -2552,8 +2614,14 @@
       <c r="Y7" s="9" t="s">
         <v>62</v>
       </c>
+      <c r="Z7" s="9">
+        <v>1</v>
+      </c>
+      <c r="AA7" s="14" t="s">
+        <v>199</v>
+      </c>
     </row>
-    <row r="8" spans="1:25" ht="108" x14ac:dyDescent="0.4">
+    <row r="8" spans="1:27" ht="108" x14ac:dyDescent="0.4">
       <c r="A8" s="4">
         <v>7</v>
       </c>
@@ -2629,8 +2697,14 @@
       <c r="Y8" s="9" t="s">
         <v>87</v>
       </c>
+      <c r="Z8" s="9">
+        <v>1</v>
+      </c>
+      <c r="AA8" s="14" t="s">
+        <v>198</v>
+      </c>
     </row>
-    <row r="9" spans="1:25" ht="61.3" x14ac:dyDescent="0.4">
+    <row r="9" spans="1:27" ht="61.3" x14ac:dyDescent="0.4">
       <c r="A9" s="4">
         <v>8</v>
       </c>
@@ -2706,8 +2780,14 @@
       <c r="Y9" s="9" t="s">
         <v>126</v>
       </c>
+      <c r="Z9" s="9">
+        <v>1</v>
+      </c>
+      <c r="AA9" s="14" t="s">
+        <v>199</v>
+      </c>
     </row>
-    <row r="10" spans="1:25" ht="136.75" x14ac:dyDescent="0.4">
+    <row r="10" spans="1:27" ht="136.75" x14ac:dyDescent="0.4">
       <c r="A10" s="4">
         <v>9</v>
       </c>
@@ -2783,8 +2863,14 @@
       <c r="Y10" s="9" t="s">
         <v>117</v>
       </c>
+      <c r="Z10" s="9">
+        <v>1</v>
+      </c>
+      <c r="AA10" s="14" t="s">
+        <v>198</v>
+      </c>
     </row>
-    <row r="11" spans="1:25" ht="92.15" x14ac:dyDescent="0.4">
+    <row r="11" spans="1:27" ht="92.15" x14ac:dyDescent="0.4">
       <c r="A11" s="4">
         <v>10</v>
       </c>
@@ -2860,8 +2946,14 @@
       <c r="Y11" s="9" t="s">
         <v>62</v>
       </c>
+      <c r="Z11" s="9">
+        <v>1</v>
+      </c>
+      <c r="AA11" s="14" t="s">
+        <v>198</v>
+      </c>
     </row>
-    <row r="12" spans="1:25" ht="92.15" x14ac:dyDescent="0.4">
+    <row r="12" spans="1:27" ht="92.15" x14ac:dyDescent="0.4">
       <c r="A12" s="4">
         <v>11</v>
       </c>
@@ -2937,8 +3029,14 @@
       <c r="Y12" s="9" t="s">
         <v>116</v>
       </c>
+      <c r="Z12" s="9">
+        <v>1</v>
+      </c>
+      <c r="AA12" s="14" t="s">
+        <v>199</v>
+      </c>
     </row>
-    <row r="13" spans="1:25" ht="76.3" x14ac:dyDescent="0.4">
+    <row r="13" spans="1:27" ht="76.3" x14ac:dyDescent="0.4">
       <c r="A13" s="4">
         <v>12</v>
       </c>
@@ -3014,8 +3112,14 @@
       <c r="Y13" s="9" t="s">
         <v>86</v>
       </c>
+      <c r="Z13" s="9">
+        <v>1</v>
+      </c>
+      <c r="AA13" s="14" t="s">
+        <v>198</v>
+      </c>
     </row>
-    <row r="14" spans="1:25" ht="139.30000000000001" x14ac:dyDescent="0.4">
+    <row r="14" spans="1:27" ht="139.30000000000001" x14ac:dyDescent="0.4">
       <c r="A14" s="4">
         <v>13</v>
       </c>
@@ -3091,8 +3195,14 @@
       <c r="Y14" s="9" t="s">
         <v>87</v>
       </c>
+      <c r="Z14" s="9">
+        <v>1</v>
+      </c>
+      <c r="AA14" s="14" t="s">
+        <v>199</v>
+      </c>
     </row>
-    <row r="15" spans="1:25" ht="122.15" x14ac:dyDescent="0.4">
+    <row r="15" spans="1:27" ht="122.15" x14ac:dyDescent="0.4">
       <c r="A15" s="4">
         <v>14</v>
       </c>
@@ -3168,8 +3278,14 @@
       <c r="Y15" s="9" t="s">
         <v>100</v>
       </c>
+      <c r="Z15" s="9">
+        <v>1</v>
+      </c>
+      <c r="AA15" s="14" t="s">
+        <v>198</v>
+      </c>
     </row>
-    <row r="16" spans="1:25" ht="124.75" x14ac:dyDescent="0.4">
+    <row r="16" spans="1:27" ht="124.75" x14ac:dyDescent="0.4">
       <c r="A16" s="4">
         <v>15</v>
       </c>
@@ -3244,6 +3360,12 @@
       </c>
       <c r="Y16" s="9" t="s">
         <v>62</v>
+      </c>
+      <c r="Z16" s="9">
+        <v>1</v>
+      </c>
+      <c r="AA16" s="14" t="s">
+        <v>199</v>
       </c>
     </row>
   </sheetData>
